--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ133"/>
+  <dimension ref="A1:AZ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137270018</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137291081</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137268911</v>
       </c>
       <c r="B4" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137271128</v>
       </c>
       <c r="B7" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137271133</v>
       </c>
       <c r="B8" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137271135</v>
       </c>
       <c r="B9" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>137271189</v>
       </c>
       <c r="B10" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137313532</v>
       </c>
       <c r="B11" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>137271137</v>
       </c>
       <c r="B12" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137268904</v>
       </c>
       <c r="B13" t="n">
-        <v>90591</v>
+        <v>90592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137291125</v>
       </c>
       <c r="B14" t="n">
-        <v>90591</v>
+        <v>90592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>137270015</v>
       </c>
       <c r="B15" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>137270016</v>
       </c>
       <c r="B16" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137270019</v>
+        <v>137270020</v>
       </c>
       <c r="B17" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702016</v>
+        <v>702043</v>
       </c>
       <c r="R17" t="n">
-        <v>6360229</v>
+        <v>6360217</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,16 +2447,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270019</t>
+          <t>https://artportalen.se/Sighting/137270020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137270020</v>
+        <v>137273122</v>
       </c>
       <c r="B18" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702043</v>
+        <v>701995</v>
       </c>
       <c r="R18" t="n">
-        <v>6360217</v>
+        <v>6359877</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,27 +2548,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270020</t>
+          <t>https://artportalen.se/Sighting/137273122</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137273122</v>
+        <v>137273123</v>
       </c>
       <c r="B19" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701995</v>
+        <v>701965</v>
       </c>
       <c r="R19" t="n">
-        <v>6359877</v>
+        <v>6359884</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,16 +2671,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273122</t>
+          <t>https://artportalen.se/Sighting/137273123</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137273123</v>
+        <v>137291996</v>
       </c>
       <c r="B20" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,14 +2708,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701965</v>
+        <v>701890</v>
       </c>
       <c r="R20" t="n">
-        <v>6359884</v>
+        <v>6360169</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,22 +2742,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,27 +2772,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273123</t>
+          <t>https://artportalen.se/Sighting/137291996</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137291996</v>
+        <v>137291999</v>
       </c>
       <c r="B21" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701890</v>
+        <v>701816</v>
       </c>
       <c r="R21" t="n">
-        <v>6360169</v>
+        <v>6360104</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,16 +2895,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291996</t>
+          <t>https://artportalen.se/Sighting/137291999</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137291999</v>
+        <v>137292003</v>
       </c>
       <c r="B22" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,13 +2936,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701816</v>
+        <v>701764</v>
       </c>
       <c r="R22" t="n">
-        <v>6360104</v>
+        <v>6360083</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,16 +3007,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291999</t>
+          <t>https://artportalen.se/Sighting/137292003</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137292003</v>
+        <v>137271140</v>
       </c>
       <c r="B23" t="n">
-        <v>87545</v>
+        <v>93323</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1988</v>
+        <v>2057</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Sandkremla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Russula torulosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701764</v>
+        <v>701797</v>
       </c>
       <c r="R23" t="n">
-        <v>6360083</v>
+        <v>6360013</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,22 +3078,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,65 +3108,68 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292003</t>
+          <t>https://artportalen.se/Sighting/137271140</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137271140</v>
+        <v>97356365</v>
       </c>
       <c r="B24" t="n">
-        <v>93322</v>
+        <v>91680</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2057</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sandkremla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Russula torulosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bres.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701797</v>
+        <v>701936</v>
       </c>
       <c r="R24" t="n">
-        <v>6360013</v>
+        <v>6360010</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,22 +3193,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,33 +3207,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271140</t>
+          <t>https://artportalen.se/Sighting/97356365</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97356365</v>
+        <v>137273109</v>
       </c>
       <c r="B25" t="n">
-        <v>91680</v>
+        <v>91935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,22 +3260,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701936</v>
+        <v>701819</v>
       </c>
       <c r="R25" t="n">
-        <v>6360010</v>
+        <v>6359992</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3305,12 +3296,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3319,56 +3320,55 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356365</t>
+          <t>https://artportalen.se/Sighting/137273109</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137273109</v>
+        <v>137270017</v>
       </c>
       <c r="B26" t="n">
-        <v>91934</v>
+        <v>91592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3215</v>
+        <v>3286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701819</v>
+        <v>702012</v>
       </c>
       <c r="R26" t="n">
-        <v>6359992</v>
+        <v>6360248</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3438,27 +3438,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273109</t>
+          <t>https://artportalen.se/Sighting/137270017</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137270017</v>
+        <v>137291992</v>
       </c>
       <c r="B27" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3484,16 +3484,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702012</v>
+        <v>701782</v>
       </c>
       <c r="R27" t="n">
-        <v>6360248</v>
+        <v>6359962</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3520,22 +3523,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,71 +3547,69 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270017</t>
+          <t>https://artportalen.se/Sighting/137291992</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137291992</v>
+        <v>137270012</v>
       </c>
       <c r="B28" t="n">
-        <v>91591</v>
+        <v>87533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3286</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701782</v>
+        <v>701760</v>
       </c>
       <c r="R28" t="n">
-        <v>6359962</v>
+        <v>6360252</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3635,22 +3636,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3659,34 +3660,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291992</t>
+          <t>https://artportalen.se/Sighting/137270012</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137270012</v>
+        <v>137270023</v>
       </c>
       <c r="B29" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701760</v>
+        <v>702157</v>
       </c>
       <c r="R29" t="n">
-        <v>6360252</v>
+        <v>6360215</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3789,16 +3789,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270012</t>
+          <t>https://artportalen.se/Sighting/137270023</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137270023</v>
+        <v>137270030</v>
       </c>
       <c r="B30" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702157</v>
+        <v>701992</v>
       </c>
       <c r="R30" t="n">
-        <v>6360215</v>
+        <v>6359879</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,16 +3901,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270023</t>
+          <t>https://artportalen.se/Sighting/137270030</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137270030</v>
+        <v>137271129</v>
       </c>
       <c r="B31" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,17 +3938,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701992</v>
+        <v>701743</v>
       </c>
       <c r="R31" t="n">
-        <v>6359879</v>
+        <v>6359954</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4002,27 +4002,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270030</t>
+          <t>https://artportalen.se/Sighting/137271129</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137271129</v>
+        <v>137273117</v>
       </c>
       <c r="B32" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701743</v>
+        <v>702059</v>
       </c>
       <c r="R32" t="n">
-        <v>6359954</v>
+        <v>6360048</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,27 +4114,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271129</t>
+          <t>https://artportalen.se/Sighting/137273117</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137273117</v>
+        <v>137273119</v>
       </c>
       <c r="B33" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702059</v>
+        <v>701965</v>
       </c>
       <c r="R33" t="n">
-        <v>6360048</v>
+        <v>6359967</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4237,16 +4237,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273117</t>
+          <t>https://artportalen.se/Sighting/137273119</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137273119</v>
+        <v>137291060</v>
       </c>
       <c r="B34" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,17 +4274,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701965</v>
+        <v>701815</v>
       </c>
       <c r="R34" t="n">
-        <v>6359967</v>
+        <v>6359943</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4308,22 +4308,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4338,27 +4328,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273119</t>
+          <t>https://artportalen.se/Sighting/137291060</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137291060</v>
+        <v>137291080</v>
       </c>
       <c r="B35" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4390,13 +4380,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701815</v>
+        <v>701869</v>
       </c>
       <c r="R35" t="n">
-        <v>6359943</v>
+        <v>6360130</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4423,9 +4413,19 @@
           <t>2026-10-16</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4440,27 +4440,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Erik Ungman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Erik Ungman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291060</t>
+          <t>https://artportalen.se/Sighting/137291080</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137291080</v>
+        <v>137291110</v>
       </c>
       <c r="B36" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4486,19 +4486,22 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701869</v>
+        <v>701884</v>
       </c>
       <c r="R36" t="n">
-        <v>6360130</v>
+        <v>6360145</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4527,7 +4530,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4537,7 +4540,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,33 +4549,34 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Ungman</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Ungman</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291080</t>
+          <t>https://artportalen.se/Sighting/137291110</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137291110</v>
+        <v>137291117</v>
       </c>
       <c r="B37" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,13 +4611,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701884</v>
+        <v>701945</v>
       </c>
       <c r="R37" t="n">
-        <v>6360145</v>
+        <v>6360267</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4642,7 +4646,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4656,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4661,7 +4665,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4679,16 +4682,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291110</t>
+          <t>https://artportalen.se/Sighting/137291117</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137291117</v>
+        <v>137291122</v>
       </c>
       <c r="B38" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4723,13 +4726,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>701945</v>
+        <v>702026</v>
       </c>
       <c r="R38" t="n">
-        <v>6360267</v>
+        <v>6360268</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4758,7 +4761,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4768,7 +4771,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,16 +4797,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291117</t>
+          <t>https://artportalen.se/Sighting/137291122</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137291122</v>
+        <v>137291990</v>
       </c>
       <c r="B39" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,22 +4832,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702026</v>
+        <v>701724</v>
       </c>
       <c r="R39" t="n">
-        <v>6360268</v>
+        <v>6359981</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,27 +4898,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291122</t>
+          <t>https://artportalen.se/Sighting/137291990</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137291990</v>
+        <v>137291991</v>
       </c>
       <c r="B40" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701724</v>
+        <v>701785</v>
       </c>
       <c r="R40" t="n">
-        <v>6359981</v>
+        <v>6359951</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5021,16 +5021,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291990</t>
+          <t>https://artportalen.se/Sighting/137291991</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137291991</v>
+        <v>137291994</v>
       </c>
       <c r="B41" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701785</v>
+        <v>701848</v>
       </c>
       <c r="R41" t="n">
-        <v>6359951</v>
+        <v>6360102</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5133,16 +5133,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291991</t>
+          <t>https://artportalen.se/Sighting/137291994</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137291994</v>
+        <v>137291998</v>
       </c>
       <c r="B42" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5174,13 +5174,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701848</v>
+        <v>701900</v>
       </c>
       <c r="R42" t="n">
-        <v>6360102</v>
+        <v>6360134</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5245,16 +5245,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291994</t>
+          <t>https://artportalen.se/Sighting/137291998</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137291998</v>
+        <v>137313537</v>
       </c>
       <c r="B43" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5282,17 +5282,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701900</v>
+        <v>701771</v>
       </c>
       <c r="R43" t="n">
-        <v>6360134</v>
+        <v>6359915</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,27 +5346,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291998</t>
+          <t>https://artportalen.se/Sighting/137313537</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137313537</v>
+        <v>137313540</v>
       </c>
       <c r="B44" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701771</v>
+        <v>701852</v>
       </c>
       <c r="R44" t="n">
-        <v>6359915</v>
+        <v>6360115</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5469,51 +5469,51 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313537</t>
+          <t>https://artportalen.se/Sighting/137313540</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137313540</v>
+        <v>137271142</v>
       </c>
       <c r="B45" t="n">
-        <v>87532</v>
+        <v>87394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701852</v>
+        <v>701805</v>
       </c>
       <c r="R45" t="n">
-        <v>6360115</v>
+        <v>6360001</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5540,22 +5540,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5570,27 +5570,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313540</t>
+          <t>https://artportalen.se/Sighting/137271142</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137271142</v>
+        <v>137291124</v>
       </c>
       <c r="B46" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5616,16 +5616,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701805</v>
+        <v>701998</v>
       </c>
       <c r="R46" t="n">
-        <v>6360001</v>
+        <v>6360085</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5652,22 +5655,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5682,65 +5685,62 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271142</t>
+          <t>https://artportalen.se/Sighting/137291124</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137291124</v>
+        <v>137270031</v>
       </c>
       <c r="B47" t="n">
-        <v>87393</v>
+        <v>87370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>701998</v>
+        <v>701939</v>
       </c>
       <c r="R47" t="n">
-        <v>6360085</v>
+        <v>6359873</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5767,22 +5767,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,27 +5797,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291124</t>
+          <t>https://artportalen.se/Sighting/137270031</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137270031</v>
+        <v>137270032</v>
       </c>
       <c r="B48" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>701939</v>
+        <v>701901</v>
       </c>
       <c r="R48" t="n">
-        <v>6359873</v>
+        <v>6359731</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5920,16 +5920,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270031</t>
+          <t>https://artportalen.se/Sighting/137270032</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137270032</v>
+        <v>137273120</v>
       </c>
       <c r="B49" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5961,13 +5961,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>701901</v>
+        <v>701966</v>
       </c>
       <c r="R49" t="n">
-        <v>6359731</v>
+        <v>6359930</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6021,27 +6021,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270032</t>
+          <t>https://artportalen.se/Sighting/137273120</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137273120</v>
+        <v>137287621</v>
       </c>
       <c r="B50" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6069,17 +6069,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>701966</v>
+        <v>701810</v>
       </c>
       <c r="R50" t="n">
-        <v>6359930</v>
+        <v>6359999</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6103,22 +6103,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6133,27 +6133,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273120</t>
+          <t>https://artportalen.se/Sighting/137287621</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137287621</v>
+        <v>137291993</v>
       </c>
       <c r="B51" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>701810</v>
+        <v>701823</v>
       </c>
       <c r="R51" t="n">
-        <v>6359999</v>
+        <v>6359978</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6245,27 +6245,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137287621</t>
+          <t>https://artportalen.se/Sighting/137291993</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137291993</v>
+        <v>137291997</v>
       </c>
       <c r="B52" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6297,13 +6297,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>701823</v>
+        <v>701890</v>
       </c>
       <c r="R52" t="n">
-        <v>6359978</v>
+        <v>6360169</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6368,16 +6368,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291993</t>
+          <t>https://artportalen.se/Sighting/137291997</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137291997</v>
+        <v>137292002</v>
       </c>
       <c r="B53" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6409,13 +6409,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>701890</v>
+        <v>701764</v>
       </c>
       <c r="R53" t="n">
-        <v>6360169</v>
+        <v>6360083</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6474,22 +6474,22 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291997</t>
+          <t>https://artportalen.se/Sighting/137292002</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137292002</v>
+        <v>137313541</v>
       </c>
       <c r="B54" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6517,17 +6517,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>701764</v>
+        <v>701928</v>
       </c>
       <c r="R54" t="n">
-        <v>6360083</v>
+        <v>6360157</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6581,27 +6581,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292002</t>
+          <t>https://artportalen.se/Sighting/137313541</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137313541</v>
+        <v>137313543</v>
       </c>
       <c r="B55" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>701928</v>
+        <v>701910</v>
       </c>
       <c r="R55" t="n">
-        <v>6360157</v>
+        <v>6360125</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6704,51 +6704,54 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313541</t>
+          <t>https://artportalen.se/Sighting/137313543</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137313543</v>
+        <v>137291127</v>
       </c>
       <c r="B56" t="n">
-        <v>87369</v>
+        <v>87615</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>701910</v>
+        <v>701898</v>
       </c>
       <c r="R56" t="n">
-        <v>6360125</v>
+        <v>6360044</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6780,7 +6783,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6790,7 +6793,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Lila fotbas</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6805,68 +6813,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell, Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313543</t>
+          <t>https://artportalen.se/Sighting/137291127</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137291127</v>
+        <v>137271130</v>
       </c>
       <c r="B57" t="n">
-        <v>87614</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3767</v>
+        <v>4188</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>701898</v>
+        <v>701748</v>
       </c>
       <c r="R57" t="n">
-        <v>6360044</v>
+        <v>6359960</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6890,27 +6895,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Lila fotbas</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6925,27 +6925,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell, Gabriella Fjordmark Lerne</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291127</t>
+          <t>https://artportalen.se/Sighting/137271130</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137271130</v>
+        <v>137271169</v>
       </c>
       <c r="B58" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6977,13 +6977,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>701748</v>
+        <v>701866</v>
       </c>
       <c r="R58" t="n">
-        <v>6359960</v>
+        <v>6359796</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7048,16 +7048,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271130</t>
+          <t>https://artportalen.se/Sighting/137271169</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137271169</v>
+        <v>137271173</v>
       </c>
       <c r="B59" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7089,13 +7089,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>701866</v>
+        <v>701847</v>
       </c>
       <c r="R59" t="n">
-        <v>6359796</v>
+        <v>6359819</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7160,16 +7160,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271169</t>
+          <t>https://artportalen.se/Sighting/137271173</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137271173</v>
+        <v>137271174</v>
       </c>
       <c r="B60" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,13 +7201,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>701847</v>
+        <v>701855</v>
       </c>
       <c r="R60" t="n">
-        <v>6359819</v>
+        <v>6359802</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7272,16 +7272,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271173</t>
+          <t>https://artportalen.se/Sighting/137271174</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137271174</v>
+        <v>137271177</v>
       </c>
       <c r="B61" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7313,13 +7313,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>701855</v>
+        <v>701846</v>
       </c>
       <c r="R61" t="n">
-        <v>6359802</v>
+        <v>6359758</v>
       </c>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7384,16 +7384,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271174</t>
+          <t>https://artportalen.se/Sighting/137271177</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137271177</v>
+        <v>137271180</v>
       </c>
       <c r="B62" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,13 +7425,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>701846</v>
+        <v>701972</v>
       </c>
       <c r="R62" t="n">
-        <v>6359758</v>
+        <v>6359691</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7496,16 +7496,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271177</t>
+          <t>https://artportalen.se/Sighting/137271180</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137271180</v>
+        <v>137291995</v>
       </c>
       <c r="B63" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7533,14 +7533,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>701972</v>
+        <v>701854</v>
       </c>
       <c r="R63" t="n">
-        <v>6359691</v>
+        <v>6360111</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7567,22 +7567,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7597,27 +7597,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271180</t>
+          <t>https://artportalen.se/Sighting/137291995</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137291995</v>
+        <v>137313538</v>
       </c>
       <c r="B64" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,17 +7645,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>701854</v>
+        <v>701851</v>
       </c>
       <c r="R64" t="n">
-        <v>6360111</v>
+        <v>6360018</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7703,33 +7703,34 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291995</t>
+          <t>https://artportalen.se/Sighting/137313538</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137313538</v>
+        <v>137270026</v>
       </c>
       <c r="B65" t="n">
-        <v>91552</v>
+        <v>93129</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7737,21 +7738,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4188</v>
+        <v>4769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7761,13 +7762,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>701851</v>
+        <v>702082</v>
       </c>
       <c r="R65" t="n">
-        <v>6360018</v>
+        <v>6360090</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7791,22 +7792,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7815,34 +7816,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313538</t>
+          <t>https://artportalen.se/Sighting/137270026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137270026</v>
+        <v>137268905</v>
       </c>
       <c r="B66" t="n">
-        <v>93128</v>
+        <v>58030</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7850,34 +7850,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>702082</v>
+        <v>702009</v>
       </c>
       <c r="R66" t="n">
-        <v>6360090</v>
+        <v>6360293</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7934,62 +7934,81 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270026</t>
+          <t>https://artportalen.se/Sighting/137268905</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137268905</v>
+        <v>129317244</v>
       </c>
       <c r="B67" t="n">
-        <v>58030</v>
+        <v>43467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>101242</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>702009</v>
+        <v>702020</v>
       </c>
       <c r="R67" t="n">
-        <v>6360293</v>
+        <v>6360085</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8016,22 +8035,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8042,88 +8051,79 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268905</t>
+          <t>https://artportalen.se/Sighting/129317244</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129317244</v>
+        <v>97357029</v>
       </c>
       <c r="B68" t="n">
-        <v>43467</v>
+        <v>5199</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>101242</v>
+        <v>105930</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>702020</v>
+        <v>701735</v>
       </c>
       <c r="R68" t="n">
-        <v>6360085</v>
+        <v>6360028</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8147,12 +8147,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8161,38 +8161,34 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, glänta.</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317244</t>
+          <t>https://artportalen.se/Sighting/97357029</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>97357029</v>
+        <v>129317281</v>
       </c>
       <c r="B69" t="n">
-        <v>5199</v>
+        <v>99147</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8200,42 +8196,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>105930</v>
+        <v>219864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>701735</v>
+        <v>701848</v>
       </c>
       <c r="R69" t="n">
-        <v>6360028</v>
+        <v>6360188</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8259,12 +8259,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8273,31 +8273,35 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97357029</t>
+          <t>https://artportalen.se/Sighting/129317281</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129317281</v>
+        <v>129317294</v>
       </c>
       <c r="B70" t="n">
         <v>99147</v>
@@ -8327,7 +8331,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8341,10 +8345,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>701848</v>
+        <v>702016</v>
       </c>
       <c r="R70" t="n">
-        <v>6360188</v>
+        <v>6360042</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8407,16 +8411,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317281</t>
+          <t>https://artportalen.se/Sighting/129317294</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129317294</v>
+        <v>137270024</v>
       </c>
       <c r="B71" t="n">
-        <v>99147</v>
+        <v>99742</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8424,46 +8428,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219864</v>
+        <v>219879</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Getrams</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Polygonatum odoratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mill.) Druce</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>702016</v>
+        <v>702138</v>
       </c>
       <c r="R71" t="n">
-        <v>6360042</v>
+        <v>6360149</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8487,12 +8482,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8503,74 +8508,69 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317294</t>
+          <t>https://artportalen.se/Sighting/137270024</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137270024</v>
+        <v>129317282</v>
       </c>
       <c r="B72" t="n">
-        <v>99741</v>
+        <v>104639</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219879</v>
+        <v>220164</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Getrams</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Polygonatum odoratum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Mill.) Druce</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>702138</v>
+        <v>701991</v>
       </c>
       <c r="R72" t="n">
-        <v>6360149</v>
+        <v>6360183</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8594,22 +8594,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8620,31 +8610,36 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270024</t>
+          <t>https://artportalen.se/Sighting/129317282</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129317282</v>
+        <v>129317299</v>
       </c>
       <c r="B73" t="n">
-        <v>104639</v>
+        <v>102224</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8652,37 +8647,46 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>701991</v>
+        <v>701900</v>
       </c>
       <c r="R73" t="n">
-        <v>6360183</v>
+        <v>6360049</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8742,16 +8746,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317282</t>
+          <t>https://artportalen.se/Sighting/129317299</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129317299</v>
+        <v>120308076</v>
       </c>
       <c r="B74" t="n">
-        <v>102224</v>
+        <v>107517</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,43 +8763,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221223</v>
+        <v>221849</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>701900</v>
+        <v>701638</v>
       </c>
       <c r="R74" t="n">
-        <v>6360049</v>
+        <v>6360226</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8822,12 +8817,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8841,7 +8836,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, glänta i gränsgata.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8852,22 +8847,22 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317299</t>
+          <t>https://artportalen.se/Sighting/120308076</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120308076</v>
+        <v>129317278</v>
       </c>
       <c r="B75" t="n">
-        <v>107517</v>
+        <v>107516</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8895,17 +8890,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>701638</v>
+        <v>701841</v>
       </c>
       <c r="R75" t="n">
-        <v>6360226</v>
+        <v>6360189</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8929,12 +8924,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8948,7 +8943,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta i gränsgata.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8959,19 +8954,19 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308076</t>
+          <t>https://artportalen.se/Sighting/129317278</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129317278</v>
+        <v>129317285</v>
       </c>
       <c r="B76" t="n">
         <v>107516</v>
@@ -9006,13 +9001,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>701841</v>
+        <v>702024</v>
       </c>
       <c r="R76" t="n">
-        <v>6360189</v>
+        <v>6360122</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9055,7 +9050,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9072,16 +9067,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317278</t>
+          <t>https://artportalen.se/Sighting/129317285</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129317285</v>
+        <v>137271151</v>
       </c>
       <c r="B77" t="n">
-        <v>107516</v>
+        <v>107835</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9109,17 +9104,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>702024</v>
+        <v>701866</v>
       </c>
       <c r="R77" t="n">
-        <v>6360122</v>
+        <v>6359934</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9143,12 +9138,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9159,36 +9164,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, myrkulle i glänta.</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317285</t>
+          <t>https://artportalen.se/Sighting/137271151</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137271151</v>
+        <v>137271158</v>
       </c>
       <c r="B78" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9220,13 +9220,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>701866</v>
+        <v>701870</v>
       </c>
       <c r="R78" t="n">
-        <v>6359934</v>
+        <v>6359895</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9291,16 +9291,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271151</t>
+          <t>https://artportalen.se/Sighting/137271158</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137271158</v>
+        <v>137273118</v>
       </c>
       <c r="B79" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9328,17 +9328,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>701870</v>
+        <v>701971</v>
       </c>
       <c r="R79" t="n">
-        <v>6359895</v>
+        <v>6359974</v>
       </c>
       <c r="S79" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9392,27 +9392,27 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271158</t>
+          <t>https://artportalen.se/Sighting/137273118</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>137273118</v>
+        <v>129317277</v>
       </c>
       <c r="B80" t="n">
-        <v>107834</v>
+        <v>102559</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9420,16 +9420,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221849</v>
+        <v>222133</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9440,17 +9440,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>701971</v>
+        <v>701841</v>
       </c>
       <c r="R80" t="n">
-        <v>6359974</v>
+        <v>6360189</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9474,22 +9474,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9500,69 +9490,74 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273118</t>
+          <t>https://artportalen.se/Sighting/129317277</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129317277</v>
+        <v>137268903</v>
       </c>
       <c r="B81" t="n">
-        <v>102559</v>
+        <v>87486</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222133</v>
+        <v>248956</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>701841</v>
+        <v>701940</v>
       </c>
       <c r="R81" t="n">
-        <v>6360189</v>
+        <v>6360261</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9586,12 +9581,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9602,36 +9607,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317277</t>
+          <t>https://artportalen.se/Sighting/137268903</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137268903</v>
+        <v>137268906</v>
       </c>
       <c r="B82" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>701940</v>
+        <v>702007</v>
       </c>
       <c r="R82" t="n">
-        <v>6360261</v>
+        <v>6360245</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9734,16 +9734,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268903</t>
+          <t>https://artportalen.se/Sighting/137268906</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>137268906</v>
+        <v>137268908</v>
       </c>
       <c r="B83" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>702007</v>
+        <v>702084</v>
       </c>
       <c r="R83" t="n">
-        <v>6360245</v>
+        <v>6360207</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9846,16 +9846,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268906</t>
+          <t>https://artportalen.se/Sighting/137268908</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>137268908</v>
+        <v>137270010</v>
       </c>
       <c r="B84" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9883,14 +9883,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>702084</v>
+        <v>701672</v>
       </c>
       <c r="R84" t="n">
-        <v>6360207</v>
+        <v>6360193</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9947,27 +9947,27 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268908</t>
+          <t>https://artportalen.se/Sighting/137270010</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>137270010</v>
+        <v>137270029</v>
       </c>
       <c r="B85" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9999,13 +9999,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>701672</v>
+        <v>701955</v>
       </c>
       <c r="R85" t="n">
-        <v>6360193</v>
+        <v>6359965</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10070,16 +10070,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270010</t>
+          <t>https://artportalen.se/Sighting/137270029</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>137270029</v>
+        <v>137270033</v>
       </c>
       <c r="B86" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10111,13 +10111,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>701955</v>
+        <v>701979</v>
       </c>
       <c r="R86" t="n">
-        <v>6359965</v>
+        <v>6359708</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10182,16 +10182,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270029</t>
+          <t>https://artportalen.se/Sighting/137270033</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>137270033</v>
+        <v>137271152</v>
       </c>
       <c r="B87" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10219,17 +10219,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>701979</v>
+        <v>701893</v>
       </c>
       <c r="R87" t="n">
-        <v>6359708</v>
+        <v>6359964</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10283,27 +10283,27 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270033</t>
+          <t>https://artportalen.se/Sighting/137271152</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>137271152</v>
+        <v>137271155</v>
       </c>
       <c r="B88" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,13 +10335,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701893</v>
+        <v>701880</v>
       </c>
       <c r="R88" t="n">
-        <v>6359964</v>
+        <v>6359914</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10406,16 +10406,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271152</t>
+          <t>https://artportalen.se/Sighting/137271155</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137271155</v>
+        <v>137271156</v>
       </c>
       <c r="B89" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10447,10 +10447,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>701880</v>
+        <v>701870</v>
       </c>
       <c r="R89" t="n">
-        <v>6359914</v>
+        <v>6359909</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10518,16 +10518,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271155</t>
+          <t>https://artportalen.se/Sighting/137271156</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>137271156</v>
+        <v>137271161</v>
       </c>
       <c r="B90" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10559,10 +10559,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>701870</v>
+        <v>701825</v>
       </c>
       <c r="R90" t="n">
-        <v>6359909</v>
+        <v>6359917</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10630,16 +10630,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271156</t>
+          <t>https://artportalen.se/Sighting/137271161</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>137271161</v>
+        <v>137271164</v>
       </c>
       <c r="B91" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>701825</v>
+        <v>701805</v>
       </c>
       <c r="R91" t="n">
-        <v>6359917</v>
+        <v>6359870</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10742,16 +10742,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271161</t>
+          <t>https://artportalen.se/Sighting/137271164</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>137271164</v>
+        <v>137271190</v>
       </c>
       <c r="B92" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10783,13 +10783,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>701805</v>
+        <v>702072</v>
       </c>
       <c r="R92" t="n">
-        <v>6359870</v>
+        <v>6359750</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10854,16 +10854,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271164</t>
+          <t>https://artportalen.se/Sighting/137271190</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>137271190</v>
+        <v>137273111</v>
       </c>
       <c r="B93" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10891,17 +10891,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>702072</v>
+        <v>701885</v>
       </c>
       <c r="R93" t="n">
-        <v>6359750</v>
+        <v>6360024</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10955,27 +10955,27 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271190</t>
+          <t>https://artportalen.se/Sighting/137273111</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>137273111</v>
+        <v>137287622</v>
       </c>
       <c r="B94" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11003,14 +11003,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>701885</v>
+        <v>701795</v>
       </c>
       <c r="R94" t="n">
-        <v>6360024</v>
+        <v>6360098</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11037,22 +11037,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11067,27 +11067,27 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273111</t>
+          <t>https://artportalen.se/Sighting/137287622</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>137287622</v>
+        <v>137292000</v>
       </c>
       <c r="B95" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11119,13 +11119,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>701795</v>
+        <v>701803</v>
       </c>
       <c r="R95" t="n">
-        <v>6360098</v>
+        <v>6360093</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11179,27 +11179,27 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137287622</t>
+          <t>https://artportalen.se/Sighting/137292000</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137292000</v>
+        <v>137292001</v>
       </c>
       <c r="B96" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>701803</v>
+        <v>701785</v>
       </c>
       <c r="R96" t="n">
-        <v>6360093</v>
+        <v>6360090</v>
       </c>
       <c r="S96" t="n">
         <v>6</v>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11296,22 +11296,22 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292000</t>
+          <t>https://artportalen.se/Sighting/137292001</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137292001</v>
+        <v>137313534</v>
       </c>
       <c r="B97" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11339,17 +11339,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>701785</v>
+        <v>701741</v>
       </c>
       <c r="R97" t="n">
-        <v>6360090</v>
+        <v>6359935</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11403,27 +11403,27 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292001</t>
+          <t>https://artportalen.se/Sighting/137313534</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137313534</v>
+        <v>137313539</v>
       </c>
       <c r="B98" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>701741</v>
+        <v>701839</v>
       </c>
       <c r="R98" t="n">
-        <v>6359935</v>
+        <v>6360044</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11526,16 +11526,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313534</t>
+          <t>https://artportalen.se/Sighting/137313539</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137313539</v>
+        <v>137313542</v>
       </c>
       <c r="B99" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>701839</v>
+        <v>701933</v>
       </c>
       <c r="R99" t="n">
-        <v>6360044</v>
+        <v>6360160</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11638,16 +11638,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313539</t>
+          <t>https://artportalen.se/Sighting/137313542</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137313542</v>
+        <v>137313544</v>
       </c>
       <c r="B100" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11679,10 +11679,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>701933</v>
+        <v>701806</v>
       </c>
       <c r="R100" t="n">
-        <v>6360160</v>
+        <v>6360084</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11750,51 +11750,51 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313542</t>
+          <t>https://artportalen.se/Sighting/137313544</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137313544</v>
+        <v>137268910</v>
       </c>
       <c r="B101" t="n">
-        <v>87485</v>
+        <v>87322</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>701806</v>
+        <v>702067</v>
       </c>
       <c r="R101" t="n">
-        <v>6360084</v>
+        <v>6360071</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11821,22 +11821,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11851,27 +11851,27 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313544</t>
+          <t>https://artportalen.se/Sighting/137268910</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137268910</v>
+        <v>137271131</v>
       </c>
       <c r="B102" t="n">
-        <v>87321</v>
+        <v>87570</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11879,37 +11879,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>702067</v>
+        <v>701753</v>
       </c>
       <c r="R102" t="n">
-        <v>6360071</v>
+        <v>6359975</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11963,27 +11963,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268910</t>
+          <t>https://artportalen.se/Sighting/137271131</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137271131</v>
+        <v>137271132</v>
       </c>
       <c r="B103" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12015,13 +12015,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>701753</v>
+        <v>701759</v>
       </c>
       <c r="R103" t="n">
-        <v>6359975</v>
+        <v>6359980</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12086,16 +12086,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271131</t>
+          <t>https://artportalen.se/Sighting/137271132</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137271132</v>
+        <v>137271138</v>
       </c>
       <c r="B104" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12127,13 +12127,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>701759</v>
+        <v>701781</v>
       </c>
       <c r="R104" t="n">
-        <v>6359980</v>
+        <v>6360015</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12198,16 +12198,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271132</t>
+          <t>https://artportalen.se/Sighting/137271138</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137271138</v>
+        <v>137271141</v>
       </c>
       <c r="B105" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12239,10 +12239,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>701781</v>
+        <v>701799</v>
       </c>
       <c r="R105" t="n">
-        <v>6360015</v>
+        <v>6360005</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12310,16 +12310,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271138</t>
+          <t>https://artportalen.se/Sighting/137271141</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137271141</v>
+        <v>137271144</v>
       </c>
       <c r="B106" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12351,10 +12351,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>701799</v>
+        <v>701811</v>
       </c>
       <c r="R106" t="n">
-        <v>6360005</v>
+        <v>6359992</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12422,16 +12422,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271141</t>
+          <t>https://artportalen.se/Sighting/137271144</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137271144</v>
+        <v>137271148</v>
       </c>
       <c r="B107" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12463,10 +12463,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>701811</v>
+        <v>701797</v>
       </c>
       <c r="R107" t="n">
-        <v>6359992</v>
+        <v>6359967</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12534,16 +12534,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271144</t>
+          <t>https://artportalen.se/Sighting/137271148</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>137271148</v>
+        <v>137271154</v>
       </c>
       <c r="B108" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12575,10 +12575,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>701797</v>
+        <v>701903</v>
       </c>
       <c r="R108" t="n">
-        <v>6359967</v>
+        <v>6359923</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12646,16 +12646,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271148</t>
+          <t>https://artportalen.se/Sighting/137271154</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>137271154</v>
+        <v>137271166</v>
       </c>
       <c r="B109" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12687,13 +12687,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>701903</v>
+        <v>701876</v>
       </c>
       <c r="R109" t="n">
-        <v>6359923</v>
+        <v>6359811</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12758,16 +12758,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271154</t>
+          <t>https://artportalen.se/Sighting/137271166</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137271166</v>
+        <v>137271167</v>
       </c>
       <c r="B110" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12799,13 +12799,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>701876</v>
+        <v>701880</v>
       </c>
       <c r="R110" t="n">
-        <v>6359811</v>
+        <v>6359800</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12870,16 +12870,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271166</t>
+          <t>https://artportalen.se/Sighting/137271167</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137271167</v>
+        <v>137271171</v>
       </c>
       <c r="B111" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>701880</v>
+        <v>701863</v>
       </c>
       <c r="R111" t="n">
-        <v>6359800</v>
+        <v>6359808</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12982,16 +12982,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271167</t>
+          <t>https://artportalen.se/Sighting/137271171</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137271171</v>
+        <v>137271172</v>
       </c>
       <c r="B112" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>701863</v>
+        <v>701835</v>
       </c>
       <c r="R112" t="n">
-        <v>6359808</v>
+        <v>6359815</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13094,16 +13094,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271171</t>
+          <t>https://artportalen.se/Sighting/137271172</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137271172</v>
+        <v>137271178</v>
       </c>
       <c r="B113" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13135,10 +13135,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>701835</v>
+        <v>701848</v>
       </c>
       <c r="R113" t="n">
-        <v>6359815</v>
+        <v>6359748</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13206,16 +13206,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271172</t>
+          <t>https://artportalen.se/Sighting/137271178</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137271178</v>
+        <v>137271179</v>
       </c>
       <c r="B114" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13247,10 +13247,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>701848</v>
+        <v>701892</v>
       </c>
       <c r="R114" t="n">
-        <v>6359748</v>
+        <v>6359714</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13318,16 +13318,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271178</t>
+          <t>https://artportalen.se/Sighting/137271179</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>137271179</v>
+        <v>137271186</v>
       </c>
       <c r="B115" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13359,10 +13359,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>701892</v>
+        <v>702010</v>
       </c>
       <c r="R115" t="n">
-        <v>6359714</v>
+        <v>6359709</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13430,16 +13430,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271179</t>
+          <t>https://artportalen.se/Sighting/137271186</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137271186</v>
+        <v>137271187</v>
       </c>
       <c r="B116" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>702010</v>
+        <v>702019</v>
       </c>
       <c r="R116" t="n">
-        <v>6359709</v>
+        <v>6359713</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13542,16 +13542,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271186</t>
+          <t>https://artportalen.se/Sighting/137271187</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137271187</v>
+        <v>137273108</v>
       </c>
       <c r="B117" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13579,14 +13579,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>702019</v>
+        <v>701798</v>
       </c>
       <c r="R117" t="n">
-        <v>6359713</v>
+        <v>6359990</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13637,33 +13637,34 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271187</t>
+          <t>https://artportalen.se/Sighting/137273108</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137273108</v>
+        <v>137273112</v>
       </c>
       <c r="B118" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13695,10 +13696,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>701798</v>
+        <v>701879</v>
       </c>
       <c r="R118" t="n">
-        <v>6359990</v>
+        <v>6360033</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13730,7 +13731,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13740,7 +13741,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13767,16 +13768,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273108</t>
+          <t>https://artportalen.se/Sighting/137273112</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137273112</v>
+        <v>137291062</v>
       </c>
       <c r="B119" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13802,16 +13803,19 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>701879</v>
+        <v>701909</v>
       </c>
       <c r="R119" t="n">
-        <v>6360033</v>
+        <v>6359993</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13838,22 +13842,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13869,27 +13863,27 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273112</t>
+          <t>https://artportalen.se/Sighting/137291062</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137291062</v>
+        <v>137291108</v>
       </c>
       <c r="B120" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13920,17 +13914,17 @@
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>701909</v>
+        <v>701834</v>
       </c>
       <c r="R120" t="n">
-        <v>6359993</v>
+        <v>6360076</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13957,9 +13951,19 @@
           <t>2026-10-16</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13975,27 +13979,27 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291062</t>
+          <t>https://artportalen.se/Sighting/137291108</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137291108</v>
+        <v>137291113</v>
       </c>
       <c r="B121" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14030,13 +14034,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>701834</v>
+        <v>701956</v>
       </c>
       <c r="R121" t="n">
-        <v>6360076</v>
+        <v>6360176</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14065,7 +14069,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14075,7 +14079,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14102,16 +14106,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291108</t>
+          <t>https://artportalen.se/Sighting/137291113</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137291113</v>
+        <v>137291120</v>
       </c>
       <c r="B122" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14146,10 +14150,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>701956</v>
+        <v>701985</v>
       </c>
       <c r="R122" t="n">
-        <v>6360176</v>
+        <v>6360293</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14181,7 +14185,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14191,7 +14195,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14218,16 +14222,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291113</t>
+          <t>https://artportalen.se/Sighting/137291120</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137291120</v>
+        <v>137312001</v>
       </c>
       <c r="B123" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14252,23 +14256,31 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>701985</v>
+        <v>701745</v>
       </c>
       <c r="R123" t="n">
-        <v>6360293</v>
+        <v>6359957</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14295,19 +14307,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14323,27 +14325,27 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Oskar Karl Elias Olsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Oskar Karl Elias Olsson, Nicolai Berg, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291120</t>
+          <t>https://artportalen.se/Sighting/137312001</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137312001</v>
+        <v>97356373</v>
       </c>
       <c r="B124" t="n">
-        <v>87569</v>
+        <v>87312</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14351,45 +14353,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>701745</v>
+        <v>701965</v>
       </c>
       <c r="R124" t="n">
-        <v>6359957</v>
+        <v>6359889</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14416,12 +14410,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14437,68 +14431,74 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson, Nicolai Berg, Meandra Sewell</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137312001</t>
+          <t>https://artportalen.se/Sighting/97356373</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>97356373</v>
+        <v>129317287</v>
       </c>
       <c r="B125" t="n">
-        <v>87312</v>
+        <v>103385</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6037417</v>
+        <v>6037533</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>701965</v>
+        <v>702037</v>
       </c>
       <c r="R125" t="n">
-        <v>6359889</v>
+        <v>6360098</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14522,12 +14522,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14536,31 +14541,35 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356373</t>
+          <t>https://artportalen.se/Sighting/129317287</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129317287</v>
+        <v>129317290</v>
       </c>
       <c r="B126" t="n">
         <v>103385</v>
@@ -14604,10 +14613,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>702037</v>
+        <v>701998</v>
       </c>
       <c r="R126" t="n">
-        <v>6360098</v>
+        <v>6360055</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14675,13 +14684,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317287</t>
+          <t>https://artportalen.se/Sighting/129317290</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129317290</v>
+        <v>129317293</v>
       </c>
       <c r="B127" t="n">
         <v>103385</v>
@@ -14725,10 +14734,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>701998</v>
+        <v>702001</v>
       </c>
       <c r="R127" t="n">
-        <v>6360055</v>
+        <v>6360045</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14765,7 +14774,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>50 cm hög, steil.</t>
+          <t>30 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14796,13 +14805,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317290</t>
+          <t>https://artportalen.se/Sighting/129317293</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129317293</v>
+        <v>129317303</v>
       </c>
       <c r="B128" t="n">
         <v>103385</v>
@@ -14846,10 +14855,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>702001</v>
+        <v>701855</v>
       </c>
       <c r="R128" t="n">
-        <v>6360045</v>
+        <v>6360068</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14886,7 +14895,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>30 cm hög, steil.</t>
+          <t>40 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14917,13 +14926,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317293</t>
+          <t>https://artportalen.se/Sighting/129317303</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129317303</v>
+        <v>129317304</v>
       </c>
       <c r="B129" t="n">
         <v>103385</v>
@@ -14967,10 +14976,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>701855</v>
+        <v>701837</v>
       </c>
       <c r="R129" t="n">
-        <v>6360068</v>
+        <v>6360008</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15038,13 +15047,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317303</t>
+          <t>https://artportalen.se/Sighting/129317304</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129317304</v>
+        <v>129317307</v>
       </c>
       <c r="B130" t="n">
         <v>103385</v>
@@ -15088,13 +15097,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>701837</v>
+        <v>701807</v>
       </c>
       <c r="R130" t="n">
-        <v>6360008</v>
+        <v>6359985</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15128,7 +15137,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>40 cm hög, steil.</t>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15159,13 +15168,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317304</t>
+          <t>https://artportalen.se/Sighting/129317307</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129317307</v>
+        <v>129317312</v>
       </c>
       <c r="B131" t="n">
         <v>103385</v>
@@ -15209,10 +15218,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>701807</v>
+        <v>701777</v>
       </c>
       <c r="R131" t="n">
-        <v>6359985</v>
+        <v>6360000</v>
       </c>
       <c r="S131" t="n">
         <v>3</v>
@@ -15249,7 +15258,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
+          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15280,13 +15289,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317307</t>
+          <t>https://artportalen.se/Sighting/129317312</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129317312</v>
+        <v>129317313</v>
       </c>
       <c r="B132" t="n">
         <v>103385</v>
@@ -15330,10 +15339,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>701777</v>
+        <v>701778</v>
       </c>
       <c r="R132" t="n">
-        <v>6360000</v>
+        <v>6359998</v>
       </c>
       <c r="S132" t="n">
         <v>3</v>
@@ -15370,7 +15379,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15400,127 +15409,6 @@
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129317312</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>129317313</v>
-      </c>
-      <c r="B133" t="n">
-        <v>103385</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>6037533</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Garderönn</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Sorbus atrata</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Ase 1:24 (4), Gtl</t>
-        </is>
-      </c>
-      <c r="Q133" t="n">
-        <v>701778</v>
-      </c>
-      <c r="R133" t="n">
-        <v>6359998</v>
-      </c>
-      <c r="S133" t="n">
-        <v>3</v>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>Lojsta</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
-        </is>
-      </c>
-      <c r="AD133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
-      </c>
-      <c r="AT133" t="inlineStr"/>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
-      <c r="AZ133" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129317313</t>
         </is>
@@ -15659,7 +15547,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ132"/>
+  <dimension ref="A1:AZ131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Ungman, Gabriella Fjordmark Lerne</t>
+          <t>Erik Ungman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137270020</v>
+        <v>137273122</v>
       </c>
       <c r="B17" t="n">
         <v>87546</v>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702043</v>
+        <v>701995</v>
       </c>
       <c r="R17" t="n">
-        <v>6360217</v>
+        <v>6359877</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,24 +2436,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270020</t>
+          <t>https://artportalen.se/Sighting/137273122</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137273122</v>
+        <v>137273123</v>
       </c>
       <c r="B18" t="n">
         <v>87546</v>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701995</v>
+        <v>701965</v>
       </c>
       <c r="R18" t="n">
-        <v>6359877</v>
+        <v>6359884</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,13 +2559,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273122</t>
+          <t>https://artportalen.se/Sighting/137273123</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137273123</v>
+        <v>137291996</v>
       </c>
       <c r="B19" t="n">
         <v>87546</v>
@@ -2596,14 +2596,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701965</v>
+        <v>701890</v>
       </c>
       <c r="R19" t="n">
-        <v>6359884</v>
+        <v>6360169</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2630,22 +2630,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,24 +2660,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273123</t>
+          <t>https://artportalen.se/Sighting/137291996</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137291996</v>
+        <v>137291999</v>
       </c>
       <c r="B20" t="n">
         <v>87546</v>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701890</v>
+        <v>701816</v>
       </c>
       <c r="R20" t="n">
-        <v>6360169</v>
+        <v>6360104</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,13 +2783,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291996</t>
+          <t>https://artportalen.se/Sighting/137291999</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137291999</v>
+        <v>137292003</v>
       </c>
       <c r="B21" t="n">
         <v>87546</v>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701816</v>
+        <v>701764</v>
       </c>
       <c r="R21" t="n">
-        <v>6360104</v>
+        <v>6360083</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,16 +2895,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291999</t>
+          <t>https://artportalen.se/Sighting/137292003</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137292003</v>
+        <v>137271140</v>
       </c>
       <c r="B22" t="n">
-        <v>87546</v>
+        <v>93323</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,37 +2912,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1988</v>
+        <v>2057</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Sandkremla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Russula torulosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701764</v>
+        <v>701797</v>
       </c>
       <c r="R22" t="n">
-        <v>6360083</v>
+        <v>6360013</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2966,22 +2966,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2996,65 +2996,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292003</t>
+          <t>https://artportalen.se/Sighting/137271140</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137271140</v>
+        <v>97356365</v>
       </c>
       <c r="B23" t="n">
-        <v>93323</v>
+        <v>91680</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2057</v>
+        <v>3215</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sandkremla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Russula torulosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bres.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701797</v>
+        <v>701936</v>
       </c>
       <c r="R23" t="n">
-        <v>6360013</v>
+        <v>6360010</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,22 +3081,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,33 +3095,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271140</t>
+          <t>https://artportalen.se/Sighting/97356365</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97356365</v>
+        <v>137273109</v>
       </c>
       <c r="B24" t="n">
-        <v>91680</v>
+        <v>91935</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,22 +3148,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701936</v>
+        <v>701819</v>
       </c>
       <c r="R24" t="n">
-        <v>6360010</v>
+        <v>6359992</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,12 +3184,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3207,56 +3208,55 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356365</t>
+          <t>https://artportalen.se/Sighting/137273109</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137273109</v>
+        <v>137270017</v>
       </c>
       <c r="B25" t="n">
-        <v>91935</v>
+        <v>91592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>3286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701819</v>
+        <v>702012</v>
       </c>
       <c r="R25" t="n">
-        <v>6359992</v>
+        <v>6360248</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3326,24 +3326,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273109</t>
+          <t>https://artportalen.se/Sighting/137270017</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137270017</v>
+        <v>137291992</v>
       </c>
       <c r="B26" t="n">
         <v>91592</v>
@@ -3372,16 +3372,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702012</v>
+        <v>701782</v>
       </c>
       <c r="R26" t="n">
-        <v>6360248</v>
+        <v>6359962</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3408,22 +3411,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3432,71 +3435,69 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270017</t>
+          <t>https://artportalen.se/Sighting/137291992</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137291992</v>
+        <v>137270012</v>
       </c>
       <c r="B27" t="n">
-        <v>91592</v>
+        <v>87533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3286</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701782</v>
+        <v>701760</v>
       </c>
       <c r="R27" t="n">
-        <v>6359962</v>
+        <v>6360252</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3523,22 +3524,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,31 +3548,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291992</t>
+          <t>https://artportalen.se/Sighting/137270012</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137270012</v>
+        <v>137270023</v>
       </c>
       <c r="B28" t="n">
         <v>87533</v>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701760</v>
+        <v>702157</v>
       </c>
       <c r="R28" t="n">
-        <v>6360252</v>
+        <v>6360215</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3677,13 +3677,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270012</t>
+          <t>https://artportalen.se/Sighting/137270023</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137270023</v>
+        <v>137270030</v>
       </c>
       <c r="B29" t="n">
         <v>87533</v>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702157</v>
+        <v>701992</v>
       </c>
       <c r="R29" t="n">
-        <v>6360215</v>
+        <v>6359879</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3789,13 +3789,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270023</t>
+          <t>https://artportalen.se/Sighting/137270030</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137270030</v>
+        <v>137271129</v>
       </c>
       <c r="B30" t="n">
         <v>87533</v>
@@ -3826,17 +3826,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701992</v>
+        <v>701743</v>
       </c>
       <c r="R30" t="n">
-        <v>6359879</v>
+        <v>6359954</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3890,24 +3890,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270030</t>
+          <t>https://artportalen.se/Sighting/137271129</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137271129</v>
+        <v>137273117</v>
       </c>
       <c r="B31" t="n">
         <v>87533</v>
@@ -3938,17 +3938,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701743</v>
+        <v>702059</v>
       </c>
       <c r="R31" t="n">
-        <v>6359954</v>
+        <v>6360048</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4002,24 +4002,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271129</t>
+          <t>https://artportalen.se/Sighting/137273117</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137273117</v>
+        <v>137273119</v>
       </c>
       <c r="B32" t="n">
         <v>87533</v>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702059</v>
+        <v>701965</v>
       </c>
       <c r="R32" t="n">
-        <v>6360048</v>
+        <v>6359967</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,13 +4125,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273117</t>
+          <t>https://artportalen.se/Sighting/137273119</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137273119</v>
+        <v>137291060</v>
       </c>
       <c r="B33" t="n">
         <v>87533</v>
@@ -4162,17 +4162,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>701965</v>
+        <v>701815</v>
       </c>
       <c r="R33" t="n">
-        <v>6359967</v>
+        <v>6359943</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4196,22 +4196,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4226,24 +4216,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273119</t>
+          <t>https://artportalen.se/Sighting/137291060</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137291060</v>
+        <v>137291080</v>
       </c>
       <c r="B34" t="n">
         <v>87533</v>
@@ -4278,13 +4268,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>701815</v>
+        <v>701869</v>
       </c>
       <c r="R34" t="n">
-        <v>6359943</v>
+        <v>6360130</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4311,9 +4301,19 @@
           <t>2026-10-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,24 +4328,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Erik Ungman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Erik Ungman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291060</t>
+          <t>https://artportalen.se/Sighting/137291080</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137291080</v>
+        <v>137291110</v>
       </c>
       <c r="B35" t="n">
         <v>87533</v>
@@ -4374,19 +4374,22 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>701869</v>
+        <v>701884</v>
       </c>
       <c r="R35" t="n">
-        <v>6360130</v>
+        <v>6360145</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4415,7 +4418,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4425,7 +4428,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4434,30 +4437,31 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Ungman</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Ungman</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291080</t>
+          <t>https://artportalen.se/Sighting/137291110</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137291110</v>
+        <v>137291117</v>
       </c>
       <c r="B36" t="n">
         <v>87533</v>
@@ -4495,13 +4499,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>701884</v>
+        <v>701945</v>
       </c>
       <c r="R36" t="n">
-        <v>6360145</v>
+        <v>6360267</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4530,7 +4534,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4540,7 +4544,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4549,7 +4553,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4567,13 +4570,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291110</t>
+          <t>https://artportalen.se/Sighting/137291117</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137291117</v>
+        <v>137291122</v>
       </c>
       <c r="B37" t="n">
         <v>87533</v>
@@ -4611,13 +4614,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>701945</v>
+        <v>702026</v>
       </c>
       <c r="R37" t="n">
-        <v>6360267</v>
+        <v>6360268</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4646,7 +4649,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4656,7 +4659,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,13 +4685,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291117</t>
+          <t>https://artportalen.se/Sighting/137291122</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137291122</v>
+        <v>137291990</v>
       </c>
       <c r="B38" t="n">
         <v>87533</v>
@@ -4717,22 +4720,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702026</v>
+        <v>701724</v>
       </c>
       <c r="R38" t="n">
-        <v>6360268</v>
+        <v>6359981</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4786,24 +4786,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291122</t>
+          <t>https://artportalen.se/Sighting/137291990</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137291990</v>
+        <v>137291991</v>
       </c>
       <c r="B39" t="n">
         <v>87533</v>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>701724</v>
+        <v>701785</v>
       </c>
       <c r="R39" t="n">
-        <v>6359981</v>
+        <v>6359951</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4909,13 +4909,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291990</t>
+          <t>https://artportalen.se/Sighting/137291991</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137291991</v>
+        <v>137291994</v>
       </c>
       <c r="B40" t="n">
         <v>87533</v>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701785</v>
+        <v>701848</v>
       </c>
       <c r="R40" t="n">
-        <v>6359951</v>
+        <v>6360102</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5021,13 +5021,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291991</t>
+          <t>https://artportalen.se/Sighting/137291994</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137291994</v>
+        <v>137291998</v>
       </c>
       <c r="B41" t="n">
         <v>87533</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701848</v>
+        <v>701900</v>
       </c>
       <c r="R41" t="n">
-        <v>6360102</v>
+        <v>6360134</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5133,13 +5133,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291994</t>
+          <t>https://artportalen.se/Sighting/137291998</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137291998</v>
+        <v>137313537</v>
       </c>
       <c r="B42" t="n">
         <v>87533</v>
@@ -5170,17 +5170,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701900</v>
+        <v>701771</v>
       </c>
       <c r="R42" t="n">
-        <v>6360134</v>
+        <v>6359915</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5234,24 +5234,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291998</t>
+          <t>https://artportalen.se/Sighting/137313537</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137313537</v>
+        <v>137313540</v>
       </c>
       <c r="B43" t="n">
         <v>87533</v>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701771</v>
+        <v>701852</v>
       </c>
       <c r="R43" t="n">
-        <v>6359915</v>
+        <v>6360115</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5357,51 +5357,51 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313537</t>
+          <t>https://artportalen.se/Sighting/137313540</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137313540</v>
+        <v>137271142</v>
       </c>
       <c r="B44" t="n">
-        <v>87533</v>
+        <v>87394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701852</v>
+        <v>701805</v>
       </c>
       <c r="R44" t="n">
-        <v>6360115</v>
+        <v>6360001</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5428,22 +5428,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5458,24 +5458,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313540</t>
+          <t>https://artportalen.se/Sighting/137271142</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137271142</v>
+        <v>137291124</v>
       </c>
       <c r="B45" t="n">
         <v>87394</v>
@@ -5504,16 +5504,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701805</v>
+        <v>701998</v>
       </c>
       <c r="R45" t="n">
-        <v>6360001</v>
+        <v>6360085</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5540,22 +5543,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5570,65 +5573,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271142</t>
+          <t>https://artportalen.se/Sighting/137291124</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137291124</v>
+        <v>137270031</v>
       </c>
       <c r="B46" t="n">
-        <v>87394</v>
+        <v>87370</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701998</v>
+        <v>701939</v>
       </c>
       <c r="R46" t="n">
-        <v>6360085</v>
+        <v>6359873</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5685,24 +5685,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291124</t>
+          <t>https://artportalen.se/Sighting/137270031</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137270031</v>
+        <v>137270032</v>
       </c>
       <c r="B47" t="n">
         <v>87370</v>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>701939</v>
+        <v>701901</v>
       </c>
       <c r="R47" t="n">
-        <v>6359873</v>
+        <v>6359731</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5808,13 +5808,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270031</t>
+          <t>https://artportalen.se/Sighting/137270032</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137270032</v>
+        <v>137273120</v>
       </c>
       <c r="B48" t="n">
         <v>87370</v>
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>701901</v>
+        <v>701966</v>
       </c>
       <c r="R48" t="n">
-        <v>6359731</v>
+        <v>6359930</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5909,24 +5909,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270032</t>
+          <t>https://artportalen.se/Sighting/137273120</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137273120</v>
+        <v>137287621</v>
       </c>
       <c r="B49" t="n">
         <v>87370</v>
@@ -5957,17 +5957,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>701966</v>
+        <v>701810</v>
       </c>
       <c r="R49" t="n">
-        <v>6359930</v>
+        <v>6359999</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5991,22 +5991,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6021,24 +6021,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273120</t>
+          <t>https://artportalen.se/Sighting/137287621</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137287621</v>
+        <v>137291993</v>
       </c>
       <c r="B50" t="n">
         <v>87370</v>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>701810</v>
+        <v>701823</v>
       </c>
       <c r="R50" t="n">
-        <v>6359999</v>
+        <v>6359978</v>
       </c>
       <c r="S50" t="n">
         <v>8</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6133,24 +6133,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137287621</t>
+          <t>https://artportalen.se/Sighting/137291993</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137291993</v>
+        <v>137291997</v>
       </c>
       <c r="B51" t="n">
         <v>87370</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>701823</v>
+        <v>701890</v>
       </c>
       <c r="R51" t="n">
-        <v>6359978</v>
+        <v>6360169</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6256,13 +6256,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291993</t>
+          <t>https://artportalen.se/Sighting/137291997</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137291997</v>
+        <v>137292002</v>
       </c>
       <c r="B52" t="n">
         <v>87370</v>
@@ -6297,13 +6297,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>701890</v>
+        <v>701764</v>
       </c>
       <c r="R52" t="n">
-        <v>6360169</v>
+        <v>6360083</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6362,19 +6362,19 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291997</t>
+          <t>https://artportalen.se/Sighting/137292002</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137292002</v>
+        <v>137313541</v>
       </c>
       <c r="B53" t="n">
         <v>87370</v>
@@ -6405,17 +6405,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>701764</v>
+        <v>701928</v>
       </c>
       <c r="R53" t="n">
-        <v>6360083</v>
+        <v>6360157</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6469,24 +6469,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292002</t>
+          <t>https://artportalen.se/Sighting/137313541</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137313541</v>
+        <v>137313543</v>
       </c>
       <c r="B54" t="n">
         <v>87370</v>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>701928</v>
+        <v>701910</v>
       </c>
       <c r="R54" t="n">
-        <v>6360157</v>
+        <v>6360125</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6592,51 +6592,54 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313541</t>
+          <t>https://artportalen.se/Sighting/137313543</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137313543</v>
+        <v>137291127</v>
       </c>
       <c r="B55" t="n">
-        <v>87370</v>
+        <v>87615</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>701910</v>
+        <v>701898</v>
       </c>
       <c r="R55" t="n">
-        <v>6360125</v>
+        <v>6360044</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6668,7 +6671,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6678,7 +6681,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Lila fotbas</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6693,68 +6701,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell, Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313543</t>
+          <t>https://artportalen.se/Sighting/137291127</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137291127</v>
+        <v>137271130</v>
       </c>
       <c r="B56" t="n">
-        <v>87615</v>
+        <v>91553</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3767</v>
+        <v>4188</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>701898</v>
+        <v>701748</v>
       </c>
       <c r="R56" t="n">
-        <v>6360044</v>
+        <v>6359960</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6778,27 +6783,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lila fotbas</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6813,24 +6813,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell, Gabriella Fjordmark Lerne</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291127</t>
+          <t>https://artportalen.se/Sighting/137271130</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137271130</v>
+        <v>137271169</v>
       </c>
       <c r="B57" t="n">
         <v>91553</v>
@@ -6865,13 +6865,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>701748</v>
+        <v>701866</v>
       </c>
       <c r="R57" t="n">
-        <v>6359960</v>
+        <v>6359796</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6936,13 +6936,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271130</t>
+          <t>https://artportalen.se/Sighting/137271169</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137271169</v>
+        <v>137271173</v>
       </c>
       <c r="B58" t="n">
         <v>91553</v>
@@ -6977,13 +6977,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>701866</v>
+        <v>701847</v>
       </c>
       <c r="R58" t="n">
-        <v>6359796</v>
+        <v>6359819</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7048,13 +7048,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271169</t>
+          <t>https://artportalen.se/Sighting/137271173</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137271173</v>
+        <v>137271174</v>
       </c>
       <c r="B59" t="n">
         <v>91553</v>
@@ -7089,13 +7089,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>701847</v>
+        <v>701855</v>
       </c>
       <c r="R59" t="n">
-        <v>6359819</v>
+        <v>6359802</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7160,13 +7160,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271173</t>
+          <t>https://artportalen.se/Sighting/137271174</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137271174</v>
+        <v>137271177</v>
       </c>
       <c r="B60" t="n">
         <v>91553</v>
@@ -7201,13 +7201,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>701855</v>
+        <v>701846</v>
       </c>
       <c r="R60" t="n">
-        <v>6359802</v>
+        <v>6359758</v>
       </c>
       <c r="S60" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7272,13 +7272,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271174</t>
+          <t>https://artportalen.se/Sighting/137271177</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137271177</v>
+        <v>137271180</v>
       </c>
       <c r="B61" t="n">
         <v>91553</v>
@@ -7313,13 +7313,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>701846</v>
+        <v>701972</v>
       </c>
       <c r="R61" t="n">
-        <v>6359758</v>
+        <v>6359691</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7384,13 +7384,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271177</t>
+          <t>https://artportalen.se/Sighting/137271180</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137271180</v>
+        <v>137291995</v>
       </c>
       <c r="B62" t="n">
         <v>91553</v>
@@ -7421,14 +7421,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>701972</v>
+        <v>701854</v>
       </c>
       <c r="R62" t="n">
-        <v>6359691</v>
+        <v>6360111</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7455,22 +7455,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7485,24 +7485,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271180</t>
+          <t>https://artportalen.se/Sighting/137291995</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137291995</v>
+        <v>137313538</v>
       </c>
       <c r="B63" t="n">
         <v>91553</v>
@@ -7533,17 +7533,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>701854</v>
+        <v>701851</v>
       </c>
       <c r="R63" t="n">
-        <v>6360111</v>
+        <v>6360018</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7591,33 +7591,34 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291995</t>
+          <t>https://artportalen.se/Sighting/137313538</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137313538</v>
+        <v>137270026</v>
       </c>
       <c r="B64" t="n">
-        <v>91553</v>
+        <v>93129</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7625,21 +7626,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4188</v>
+        <v>4769</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7649,13 +7650,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>701851</v>
+        <v>702082</v>
       </c>
       <c r="R64" t="n">
-        <v>6360018</v>
+        <v>6360090</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7679,22 +7680,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7703,34 +7704,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313538</t>
+          <t>https://artportalen.se/Sighting/137270026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137270026</v>
+        <v>137268905</v>
       </c>
       <c r="B65" t="n">
-        <v>93129</v>
+        <v>58030</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7738,34 +7738,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>702082</v>
+        <v>702009</v>
       </c>
       <c r="R65" t="n">
-        <v>6360090</v>
+        <v>6360293</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,62 +7822,81 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270026</t>
+          <t>https://artportalen.se/Sighting/137268905</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137268905</v>
+        <v>129317244</v>
       </c>
       <c r="B66" t="n">
-        <v>58030</v>
+        <v>43467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>101242</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>702009</v>
+        <v>702020</v>
       </c>
       <c r="R66" t="n">
-        <v>6360293</v>
+        <v>6360085</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7904,22 +7923,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7930,88 +7939,79 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268905</t>
+          <t>https://artportalen.se/Sighting/129317244</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129317244</v>
+        <v>97357029</v>
       </c>
       <c r="B67" t="n">
-        <v>43467</v>
+        <v>5199</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>101242</v>
+        <v>105930</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>702020</v>
+        <v>701735</v>
       </c>
       <c r="R67" t="n">
-        <v>6360085</v>
+        <v>6360028</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8049,38 +8049,34 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, glänta.</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317244</t>
+          <t>https://artportalen.se/Sighting/97357029</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>97357029</v>
+        <v>129317281</v>
       </c>
       <c r="B68" t="n">
-        <v>5199</v>
+        <v>99147</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8088,42 +8084,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>105930</v>
+        <v>219864</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>701735</v>
+        <v>701848</v>
       </c>
       <c r="R68" t="n">
-        <v>6360028</v>
+        <v>6360188</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8147,12 +8147,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8161,31 +8161,35 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97357029</t>
+          <t>https://artportalen.se/Sighting/129317281</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129317281</v>
+        <v>129317294</v>
       </c>
       <c r="B69" t="n">
         <v>99147</v>
@@ -8215,7 +8219,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8229,10 +8233,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>701848</v>
+        <v>702016</v>
       </c>
       <c r="R69" t="n">
-        <v>6360188</v>
+        <v>6360042</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8295,16 +8299,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317281</t>
+          <t>https://artportalen.se/Sighting/129317294</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129317294</v>
+        <v>137270024</v>
       </c>
       <c r="B70" t="n">
-        <v>99147</v>
+        <v>99742</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8312,46 +8316,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219864</v>
+        <v>219879</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Getrams</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Polygonatum odoratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mill.) Druce</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>702016</v>
+        <v>702138</v>
       </c>
       <c r="R70" t="n">
-        <v>6360042</v>
+        <v>6360149</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8375,12 +8370,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8391,74 +8396,69 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317294</t>
+          <t>https://artportalen.se/Sighting/137270024</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137270024</v>
+        <v>129317282</v>
       </c>
       <c r="B71" t="n">
-        <v>99742</v>
+        <v>104639</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219879</v>
+        <v>220164</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Getrams</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Polygonatum odoratum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Mill.) Druce</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>702138</v>
+        <v>701991</v>
       </c>
       <c r="R71" t="n">
-        <v>6360149</v>
+        <v>6360183</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8482,22 +8482,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8508,31 +8498,36 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270024</t>
+          <t>https://artportalen.se/Sighting/129317282</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129317282</v>
+        <v>129317299</v>
       </c>
       <c r="B72" t="n">
-        <v>104639</v>
+        <v>102224</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8540,37 +8535,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>701991</v>
+        <v>701900</v>
       </c>
       <c r="R72" t="n">
-        <v>6360183</v>
+        <v>6360049</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8630,16 +8634,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317282</t>
+          <t>https://artportalen.se/Sighting/129317299</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129317299</v>
+        <v>120308076</v>
       </c>
       <c r="B73" t="n">
-        <v>102224</v>
+        <v>107517</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8647,43 +8651,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221223</v>
+        <v>221849</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>701900</v>
+        <v>701638</v>
       </c>
       <c r="R73" t="n">
-        <v>6360049</v>
+        <v>6360226</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8710,12 +8705,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8729,7 +8724,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, glänta i gränsgata.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8740,22 +8735,22 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317299</t>
+          <t>https://artportalen.se/Sighting/120308076</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120308076</v>
+        <v>129317278</v>
       </c>
       <c r="B74" t="n">
-        <v>107517</v>
+        <v>107516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8783,17 +8778,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>701638</v>
+        <v>701841</v>
       </c>
       <c r="R74" t="n">
-        <v>6360226</v>
+        <v>6360189</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8817,12 +8812,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8836,7 +8831,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta i gränsgata.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8847,19 +8842,19 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308076</t>
+          <t>https://artportalen.se/Sighting/129317278</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129317278</v>
+        <v>129317285</v>
       </c>
       <c r="B75" t="n">
         <v>107516</v>
@@ -8894,13 +8889,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>701841</v>
+        <v>702024</v>
       </c>
       <c r="R75" t="n">
-        <v>6360189</v>
+        <v>6360122</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8943,7 +8938,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8960,16 +8955,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317278</t>
+          <t>https://artportalen.se/Sighting/129317285</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129317285</v>
+        <v>137271151</v>
       </c>
       <c r="B76" t="n">
-        <v>107516</v>
+        <v>107835</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8997,17 +8992,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>702024</v>
+        <v>701866</v>
       </c>
       <c r="R76" t="n">
-        <v>6360122</v>
+        <v>6359934</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9031,12 +9026,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9047,33 +9052,28 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, myrkulle i glänta.</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317285</t>
+          <t>https://artportalen.se/Sighting/137271151</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137271151</v>
+        <v>137271158</v>
       </c>
       <c r="B77" t="n">
         <v>107835</v>
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>701866</v>
+        <v>701870</v>
       </c>
       <c r="R77" t="n">
-        <v>6359934</v>
+        <v>6359895</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9179,13 +9179,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271151</t>
+          <t>https://artportalen.se/Sighting/137271158</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137271158</v>
+        <v>137273118</v>
       </c>
       <c r="B78" t="n">
         <v>107835</v>
@@ -9216,17 +9216,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>701870</v>
+        <v>701971</v>
       </c>
       <c r="R78" t="n">
-        <v>6359895</v>
+        <v>6359974</v>
       </c>
       <c r="S78" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9280,27 +9280,27 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271158</t>
+          <t>https://artportalen.se/Sighting/137273118</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137273118</v>
+        <v>129317277</v>
       </c>
       <c r="B79" t="n">
-        <v>107835</v>
+        <v>102559</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9308,16 +9308,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221849</v>
+        <v>222133</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9328,17 +9328,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>701971</v>
+        <v>701841</v>
       </c>
       <c r="R79" t="n">
-        <v>6359974</v>
+        <v>6360189</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9362,22 +9362,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9388,69 +9378,74 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273118</t>
+          <t>https://artportalen.se/Sighting/129317277</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129317277</v>
+        <v>137268903</v>
       </c>
       <c r="B80" t="n">
-        <v>102559</v>
+        <v>87486</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222133</v>
+        <v>248956</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>701841</v>
+        <v>701940</v>
       </c>
       <c r="R80" t="n">
-        <v>6360189</v>
+        <v>6360261</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9474,12 +9469,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9490,33 +9495,28 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317277</t>
+          <t>https://artportalen.se/Sighting/137268903</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>137268903</v>
+        <v>137268906</v>
       </c>
       <c r="B81" t="n">
         <v>87486</v>
@@ -9551,10 +9551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>701940</v>
+        <v>702007</v>
       </c>
       <c r="R81" t="n">
-        <v>6360261</v>
+        <v>6360245</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9622,13 +9622,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268903</t>
+          <t>https://artportalen.se/Sighting/137268906</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137268906</v>
+        <v>137268908</v>
       </c>
       <c r="B82" t="n">
         <v>87486</v>
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>702007</v>
+        <v>702084</v>
       </c>
       <c r="R82" t="n">
-        <v>6360245</v>
+        <v>6360207</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9734,13 +9734,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268906</t>
+          <t>https://artportalen.se/Sighting/137268908</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>137268908</v>
+        <v>137270010</v>
       </c>
       <c r="B83" t="n">
         <v>87486</v>
@@ -9771,14 +9771,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>702084</v>
+        <v>701672</v>
       </c>
       <c r="R83" t="n">
-        <v>6360207</v>
+        <v>6360193</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9835,24 +9835,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268908</t>
+          <t>https://artportalen.se/Sighting/137270010</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>137270010</v>
+        <v>137270029</v>
       </c>
       <c r="B84" t="n">
         <v>87486</v>
@@ -9887,13 +9887,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>701672</v>
+        <v>701955</v>
       </c>
       <c r="R84" t="n">
-        <v>6360193</v>
+        <v>6359965</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9958,13 +9958,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270010</t>
+          <t>https://artportalen.se/Sighting/137270029</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>137270029</v>
+        <v>137270033</v>
       </c>
       <c r="B85" t="n">
         <v>87486</v>
@@ -9999,13 +9999,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>701955</v>
+        <v>701979</v>
       </c>
       <c r="R85" t="n">
-        <v>6359965</v>
+        <v>6359708</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10070,13 +10070,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270029</t>
+          <t>https://artportalen.se/Sighting/137270033</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>137270033</v>
+        <v>137271152</v>
       </c>
       <c r="B86" t="n">
         <v>87486</v>
@@ -10107,17 +10107,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>701979</v>
+        <v>701893</v>
       </c>
       <c r="R86" t="n">
-        <v>6359708</v>
+        <v>6359964</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10171,24 +10171,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270033</t>
+          <t>https://artportalen.se/Sighting/137271152</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>137271152</v>
+        <v>137271155</v>
       </c>
       <c r="B87" t="n">
         <v>87486</v>
@@ -10223,13 +10223,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>701893</v>
+        <v>701880</v>
       </c>
       <c r="R87" t="n">
-        <v>6359964</v>
+        <v>6359914</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10294,13 +10294,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271152</t>
+          <t>https://artportalen.se/Sighting/137271155</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>137271155</v>
+        <v>137271156</v>
       </c>
       <c r="B88" t="n">
         <v>87486</v>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701880</v>
+        <v>701870</v>
       </c>
       <c r="R88" t="n">
-        <v>6359914</v>
+        <v>6359909</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10406,13 +10406,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271155</t>
+          <t>https://artportalen.se/Sighting/137271156</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137271156</v>
+        <v>137271161</v>
       </c>
       <c r="B89" t="n">
         <v>87486</v>
@@ -10447,10 +10447,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>701870</v>
+        <v>701825</v>
       </c>
       <c r="R89" t="n">
-        <v>6359909</v>
+        <v>6359917</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10518,13 +10518,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271156</t>
+          <t>https://artportalen.se/Sighting/137271161</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>137271161</v>
+        <v>137271164</v>
       </c>
       <c r="B90" t="n">
         <v>87486</v>
@@ -10559,10 +10559,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>701825</v>
+        <v>701805</v>
       </c>
       <c r="R90" t="n">
-        <v>6359917</v>
+        <v>6359870</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10630,13 +10630,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271161</t>
+          <t>https://artportalen.se/Sighting/137271164</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>137271164</v>
+        <v>137271190</v>
       </c>
       <c r="B91" t="n">
         <v>87486</v>
@@ -10671,13 +10671,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>701805</v>
+        <v>702072</v>
       </c>
       <c r="R91" t="n">
-        <v>6359870</v>
+        <v>6359750</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10742,13 +10742,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271164</t>
+          <t>https://artportalen.se/Sighting/137271190</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>137271190</v>
+        <v>137273111</v>
       </c>
       <c r="B92" t="n">
         <v>87486</v>
@@ -10779,17 +10779,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>702072</v>
+        <v>701885</v>
       </c>
       <c r="R92" t="n">
-        <v>6359750</v>
+        <v>6360024</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10843,24 +10843,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271190</t>
+          <t>https://artportalen.se/Sighting/137273111</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>137273111</v>
+        <v>137287622</v>
       </c>
       <c r="B93" t="n">
         <v>87486</v>
@@ -10891,14 +10891,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>701885</v>
+        <v>701795</v>
       </c>
       <c r="R93" t="n">
-        <v>6360024</v>
+        <v>6360098</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10925,22 +10925,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10955,24 +10955,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273111</t>
+          <t>https://artportalen.se/Sighting/137287622</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>137287622</v>
+        <v>137292000</v>
       </c>
       <c r="B94" t="n">
         <v>87486</v>
@@ -11007,13 +11007,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>701795</v>
+        <v>701803</v>
       </c>
       <c r="R94" t="n">
-        <v>6360098</v>
+        <v>6360093</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11067,24 +11067,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137287622</t>
+          <t>https://artportalen.se/Sighting/137292000</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>137292000</v>
+        <v>137292001</v>
       </c>
       <c r="B95" t="n">
         <v>87486</v>
@@ -11119,10 +11119,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>701803</v>
+        <v>701785</v>
       </c>
       <c r="R95" t="n">
-        <v>6360093</v>
+        <v>6360090</v>
       </c>
       <c r="S95" t="n">
         <v>6</v>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11184,19 +11184,19 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292000</t>
+          <t>https://artportalen.se/Sighting/137292001</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137292001</v>
+        <v>137313534</v>
       </c>
       <c r="B96" t="n">
         <v>87486</v>
@@ -11227,17 +11227,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>701785</v>
+        <v>701741</v>
       </c>
       <c r="R96" t="n">
-        <v>6360090</v>
+        <v>6359935</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11291,24 +11291,24 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292001</t>
+          <t>https://artportalen.se/Sighting/137313534</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137313534</v>
+        <v>137313539</v>
       </c>
       <c r="B97" t="n">
         <v>87486</v>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>701741</v>
+        <v>701839</v>
       </c>
       <c r="R97" t="n">
-        <v>6359935</v>
+        <v>6360044</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11414,13 +11414,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313534</t>
+          <t>https://artportalen.se/Sighting/137313539</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137313539</v>
+        <v>137313542</v>
       </c>
       <c r="B98" t="n">
         <v>87486</v>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>701839</v>
+        <v>701933</v>
       </c>
       <c r="R98" t="n">
-        <v>6360044</v>
+        <v>6360160</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11526,13 +11526,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313539</t>
+          <t>https://artportalen.se/Sighting/137313542</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137313542</v>
+        <v>137313544</v>
       </c>
       <c r="B99" t="n">
         <v>87486</v>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>701933</v>
+        <v>701806</v>
       </c>
       <c r="R99" t="n">
-        <v>6360160</v>
+        <v>6360084</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11638,51 +11638,51 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313542</t>
+          <t>https://artportalen.se/Sighting/137313544</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137313544</v>
+        <v>137268910</v>
       </c>
       <c r="B100" t="n">
-        <v>87486</v>
+        <v>87322</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>701806</v>
+        <v>702067</v>
       </c>
       <c r="R100" t="n">
-        <v>6360084</v>
+        <v>6360071</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11709,22 +11709,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11739,27 +11739,27 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313544</t>
+          <t>https://artportalen.se/Sighting/137268910</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137268910</v>
+        <v>137271131</v>
       </c>
       <c r="B101" t="n">
-        <v>87322</v>
+        <v>87570</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11767,37 +11767,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>702067</v>
+        <v>701753</v>
       </c>
       <c r="R101" t="n">
-        <v>6360071</v>
+        <v>6359975</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11851,24 +11851,24 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268910</t>
+          <t>https://artportalen.se/Sighting/137271131</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137271131</v>
+        <v>137271132</v>
       </c>
       <c r="B102" t="n">
         <v>87570</v>
@@ -11903,13 +11903,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>701753</v>
+        <v>701759</v>
       </c>
       <c r="R102" t="n">
-        <v>6359975</v>
+        <v>6359980</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11974,13 +11974,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271131</t>
+          <t>https://artportalen.se/Sighting/137271132</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137271132</v>
+        <v>137271138</v>
       </c>
       <c r="B103" t="n">
         <v>87570</v>
@@ -12015,13 +12015,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>701759</v>
+        <v>701781</v>
       </c>
       <c r="R103" t="n">
-        <v>6359980</v>
+        <v>6360015</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12086,13 +12086,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271132</t>
+          <t>https://artportalen.se/Sighting/137271138</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137271138</v>
+        <v>137271141</v>
       </c>
       <c r="B104" t="n">
         <v>87570</v>
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>701781</v>
+        <v>701799</v>
       </c>
       <c r="R104" t="n">
-        <v>6360015</v>
+        <v>6360005</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12198,13 +12198,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271138</t>
+          <t>https://artportalen.se/Sighting/137271141</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137271141</v>
+        <v>137271144</v>
       </c>
       <c r="B105" t="n">
         <v>87570</v>
@@ -12239,10 +12239,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>701799</v>
+        <v>701811</v>
       </c>
       <c r="R105" t="n">
-        <v>6360005</v>
+        <v>6359992</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12310,13 +12310,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271141</t>
+          <t>https://artportalen.se/Sighting/137271144</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137271144</v>
+        <v>137271148</v>
       </c>
       <c r="B106" t="n">
         <v>87570</v>
@@ -12351,10 +12351,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>701811</v>
+        <v>701797</v>
       </c>
       <c r="R106" t="n">
-        <v>6359992</v>
+        <v>6359967</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12422,13 +12422,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271144</t>
+          <t>https://artportalen.se/Sighting/137271148</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137271148</v>
+        <v>137271154</v>
       </c>
       <c r="B107" t="n">
         <v>87570</v>
@@ -12463,10 +12463,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>701797</v>
+        <v>701903</v>
       </c>
       <c r="R107" t="n">
-        <v>6359967</v>
+        <v>6359923</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12534,13 +12534,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271148</t>
+          <t>https://artportalen.se/Sighting/137271154</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>137271154</v>
+        <v>137271166</v>
       </c>
       <c r="B108" t="n">
         <v>87570</v>
@@ -12575,13 +12575,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>701903</v>
+        <v>701876</v>
       </c>
       <c r="R108" t="n">
-        <v>6359923</v>
+        <v>6359811</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12646,13 +12646,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271154</t>
+          <t>https://artportalen.se/Sighting/137271166</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>137271166</v>
+        <v>137271167</v>
       </c>
       <c r="B109" t="n">
         <v>87570</v>
@@ -12687,13 +12687,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>701876</v>
+        <v>701880</v>
       </c>
       <c r="R109" t="n">
-        <v>6359811</v>
+        <v>6359800</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12758,13 +12758,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271166</t>
+          <t>https://artportalen.se/Sighting/137271167</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137271167</v>
+        <v>137271171</v>
       </c>
       <c r="B110" t="n">
         <v>87570</v>
@@ -12799,10 +12799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>701880</v>
+        <v>701863</v>
       </c>
       <c r="R110" t="n">
-        <v>6359800</v>
+        <v>6359808</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12870,13 +12870,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271167</t>
+          <t>https://artportalen.se/Sighting/137271171</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137271171</v>
+        <v>137271172</v>
       </c>
       <c r="B111" t="n">
         <v>87570</v>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>701863</v>
+        <v>701835</v>
       </c>
       <c r="R111" t="n">
-        <v>6359808</v>
+        <v>6359815</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12982,13 +12982,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271171</t>
+          <t>https://artportalen.se/Sighting/137271172</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137271172</v>
+        <v>137271178</v>
       </c>
       <c r="B112" t="n">
         <v>87570</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>701835</v>
+        <v>701848</v>
       </c>
       <c r="R112" t="n">
-        <v>6359815</v>
+        <v>6359748</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13094,13 +13094,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271172</t>
+          <t>https://artportalen.se/Sighting/137271178</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137271178</v>
+        <v>137271179</v>
       </c>
       <c r="B113" t="n">
         <v>87570</v>
@@ -13135,10 +13135,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>701848</v>
+        <v>701892</v>
       </c>
       <c r="R113" t="n">
-        <v>6359748</v>
+        <v>6359714</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13206,13 +13206,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271178</t>
+          <t>https://artportalen.se/Sighting/137271179</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137271179</v>
+        <v>137271186</v>
       </c>
       <c r="B114" t="n">
         <v>87570</v>
@@ -13247,10 +13247,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>701892</v>
+        <v>702010</v>
       </c>
       <c r="R114" t="n">
-        <v>6359714</v>
+        <v>6359709</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13318,13 +13318,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271179</t>
+          <t>https://artportalen.se/Sighting/137271186</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>137271186</v>
+        <v>137271187</v>
       </c>
       <c r="B115" t="n">
         <v>87570</v>
@@ -13359,10 +13359,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>702010</v>
+        <v>702019</v>
       </c>
       <c r="R115" t="n">
-        <v>6359709</v>
+        <v>6359713</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13430,13 +13430,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271186</t>
+          <t>https://artportalen.se/Sighting/137271187</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137271187</v>
+        <v>137273108</v>
       </c>
       <c r="B116" t="n">
         <v>87570</v>
@@ -13467,14 +13467,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>702019</v>
+        <v>701798</v>
       </c>
       <c r="R116" t="n">
-        <v>6359713</v>
+        <v>6359990</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13525,30 +13525,31 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271187</t>
+          <t>https://artportalen.se/Sighting/137273108</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137273108</v>
+        <v>137273112</v>
       </c>
       <c r="B117" t="n">
         <v>87570</v>
@@ -13583,10 +13584,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>701798</v>
+        <v>701879</v>
       </c>
       <c r="R117" t="n">
-        <v>6359990</v>
+        <v>6360033</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13618,7 +13619,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13628,7 +13629,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13655,13 +13656,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273108</t>
+          <t>https://artportalen.se/Sighting/137273112</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137273112</v>
+        <v>137291062</v>
       </c>
       <c r="B118" t="n">
         <v>87570</v>
@@ -13690,16 +13691,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>701879</v>
+        <v>701909</v>
       </c>
       <c r="R118" t="n">
-        <v>6360033</v>
+        <v>6359993</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13726,22 +13730,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13757,24 +13751,24 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273112</t>
+          <t>https://artportalen.se/Sighting/137291062</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137291062</v>
+        <v>137291108</v>
       </c>
       <c r="B119" t="n">
         <v>87570</v>
@@ -13808,17 +13802,17 @@
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>701909</v>
+        <v>701834</v>
       </c>
       <c r="R119" t="n">
-        <v>6359993</v>
+        <v>6360076</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13845,9 +13839,19 @@
           <t>2026-10-16</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13863,24 +13867,24 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291062</t>
+          <t>https://artportalen.se/Sighting/137291108</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137291108</v>
+        <v>137291113</v>
       </c>
       <c r="B120" t="n">
         <v>87570</v>
@@ -13918,13 +13922,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>701834</v>
+        <v>701956</v>
       </c>
       <c r="R120" t="n">
-        <v>6360076</v>
+        <v>6360176</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13953,7 +13957,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13963,7 +13967,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13990,13 +13994,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291108</t>
+          <t>https://artportalen.se/Sighting/137291113</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137291113</v>
+        <v>137291120</v>
       </c>
       <c r="B121" t="n">
         <v>87570</v>
@@ -14034,10 +14038,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>701956</v>
+        <v>701985</v>
       </c>
       <c r="R121" t="n">
-        <v>6360176</v>
+        <v>6360293</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14069,7 +14073,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14079,7 +14083,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14106,13 +14110,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291113</t>
+          <t>https://artportalen.se/Sighting/137291120</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137291120</v>
+        <v>137312001</v>
       </c>
       <c r="B122" t="n">
         <v>87570</v>
@@ -14140,23 +14144,31 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>701985</v>
+        <v>701745</v>
       </c>
       <c r="R122" t="n">
-        <v>6360293</v>
+        <v>6359957</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14183,19 +14195,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14211,27 +14213,27 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Oskar Karl Elias Olsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Oskar Karl Elias Olsson, Nicolai Berg, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291120</t>
+          <t>https://artportalen.se/Sighting/137312001</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137312001</v>
+        <v>97356373</v>
       </c>
       <c r="B123" t="n">
-        <v>87570</v>
+        <v>87312</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14239,45 +14241,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>701745</v>
+        <v>701965</v>
       </c>
       <c r="R123" t="n">
-        <v>6359957</v>
+        <v>6359889</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14304,12 +14298,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14325,68 +14319,74 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson, Nicolai Berg, Meandra Sewell</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137312001</t>
+          <t>https://artportalen.se/Sighting/97356373</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>97356373</v>
+        <v>129317287</v>
       </c>
       <c r="B124" t="n">
-        <v>87312</v>
+        <v>103385</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6037417</v>
+        <v>6037533</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>701965</v>
+        <v>702037</v>
       </c>
       <c r="R124" t="n">
-        <v>6359889</v>
+        <v>6360098</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14410,12 +14410,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14424,31 +14429,35 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356373</t>
+          <t>https://artportalen.se/Sighting/129317287</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129317287</v>
+        <v>129317290</v>
       </c>
       <c r="B125" t="n">
         <v>103385</v>
@@ -14492,10 +14501,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>702037</v>
+        <v>701998</v>
       </c>
       <c r="R125" t="n">
-        <v>6360098</v>
+        <v>6360055</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14563,13 +14572,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317287</t>
+          <t>https://artportalen.se/Sighting/129317290</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129317290</v>
+        <v>129317293</v>
       </c>
       <c r="B126" t="n">
         <v>103385</v>
@@ -14613,10 +14622,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>701998</v>
+        <v>702001</v>
       </c>
       <c r="R126" t="n">
-        <v>6360055</v>
+        <v>6360045</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14653,7 +14662,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>50 cm hög, steil.</t>
+          <t>30 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14684,13 +14693,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317290</t>
+          <t>https://artportalen.se/Sighting/129317293</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129317293</v>
+        <v>129317303</v>
       </c>
       <c r="B127" t="n">
         <v>103385</v>
@@ -14734,10 +14743,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>702001</v>
+        <v>701855</v>
       </c>
       <c r="R127" t="n">
-        <v>6360045</v>
+        <v>6360068</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14774,7 +14783,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>30 cm hög, steil.</t>
+          <t>40 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14805,13 +14814,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317293</t>
+          <t>https://artportalen.se/Sighting/129317303</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129317303</v>
+        <v>129317304</v>
       </c>
       <c r="B128" t="n">
         <v>103385</v>
@@ -14855,10 +14864,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>701855</v>
+        <v>701837</v>
       </c>
       <c r="R128" t="n">
-        <v>6360068</v>
+        <v>6360008</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14926,13 +14935,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317303</t>
+          <t>https://artportalen.se/Sighting/129317304</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129317304</v>
+        <v>129317307</v>
       </c>
       <c r="B129" t="n">
         <v>103385</v>
@@ -14976,13 +14985,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>701837</v>
+        <v>701807</v>
       </c>
       <c r="R129" t="n">
-        <v>6360008</v>
+        <v>6359985</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15016,7 +15025,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>40 cm hög, steil.</t>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15047,13 +15056,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317304</t>
+          <t>https://artportalen.se/Sighting/129317307</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129317307</v>
+        <v>129317312</v>
       </c>
       <c r="B130" t="n">
         <v>103385</v>
@@ -15097,10 +15106,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>701807</v>
+        <v>701777</v>
       </c>
       <c r="R130" t="n">
-        <v>6359985</v>
+        <v>6360000</v>
       </c>
       <c r="S130" t="n">
         <v>3</v>
@@ -15137,7 +15146,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
+          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15168,13 +15177,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317307</t>
+          <t>https://artportalen.se/Sighting/129317312</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129317312</v>
+        <v>129317313</v>
       </c>
       <c r="B131" t="n">
         <v>103385</v>
@@ -15218,10 +15227,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>701777</v>
+        <v>701778</v>
       </c>
       <c r="R131" t="n">
-        <v>6360000</v>
+        <v>6359998</v>
       </c>
       <c r="S131" t="n">
         <v>3</v>
@@ -15258,7 +15267,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15288,127 +15297,6 @@
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/129317312</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>129317313</v>
-      </c>
-      <c r="B132" t="n">
-        <v>103385</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>6037533</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Garderönn</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Sorbus atrata</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>Ase 1:24 (4), Gtl</t>
-        </is>
-      </c>
-      <c r="Q132" t="n">
-        <v>701778</v>
-      </c>
-      <c r="R132" t="n">
-        <v>6359998</v>
-      </c>
-      <c r="S132" t="n">
-        <v>3</v>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>Lojsta</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
-        </is>
-      </c>
-      <c r="AD132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
-      </c>
-      <c r="AT132" t="inlineStr"/>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
-      <c r="AZ132" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129317313</t>
         </is>
@@ -15546,7 +15434,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270018</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137291081</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137268911</v>
       </c>
       <c r="B4" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137271128</v>
       </c>
       <c r="B7" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137271133</v>
       </c>
       <c r="B8" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137271135</v>
       </c>
       <c r="B9" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>137271189</v>
       </c>
       <c r="B10" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137313532</v>
       </c>
       <c r="B11" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>137271137</v>
       </c>
       <c r="B12" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137268904</v>
       </c>
       <c r="B13" t="n">
-        <v>90592</v>
+        <v>90595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137291125</v>
       </c>
       <c r="B14" t="n">
-        <v>90592</v>
+        <v>90595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>137270015</v>
       </c>
       <c r="B15" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>137270016</v>
       </c>
       <c r="B16" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>137273122</v>
       </c>
       <c r="B17" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>137273123</v>
       </c>
       <c r="B18" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137291996</v>
       </c>
       <c r="B19" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>137291999</v>
       </c>
       <c r="B20" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>137292003</v>
       </c>
       <c r="B21" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>137271140</v>
       </c>
       <c r="B22" t="n">
-        <v>93323</v>
+        <v>93328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>137273109</v>
       </c>
       <c r="B24" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137270017</v>
       </c>
       <c r="B25" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137291992</v>
       </c>
       <c r="B26" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>137270012</v>
       </c>
       <c r="B27" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137270023</v>
       </c>
       <c r="B28" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>137270030</v>
       </c>
       <c r="B29" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>137271129</v>
       </c>
       <c r="B30" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>137273117</v>
       </c>
       <c r="B31" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>137273119</v>
       </c>
       <c r="B32" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137291060</v>
       </c>
       <c r="B33" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>137291080</v>
       </c>
       <c r="B34" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137291110</v>
       </c>
       <c r="B35" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>137291117</v>
       </c>
       <c r="B36" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>137291122</v>
       </c>
       <c r="B37" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>137291990</v>
       </c>
       <c r="B38" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>137291991</v>
       </c>
       <c r="B39" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>137291994</v>
       </c>
       <c r="B40" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>137291998</v>
       </c>
       <c r="B41" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>137313537</v>
       </c>
       <c r="B42" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>137313540</v>
       </c>
       <c r="B43" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>137271142</v>
       </c>
       <c r="B44" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>137291124</v>
       </c>
       <c r="B45" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137270031</v>
       </c>
       <c r="B46" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>137270032</v>
       </c>
       <c r="B47" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>137273120</v>
       </c>
       <c r="B48" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>137287621</v>
       </c>
       <c r="B49" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137291993</v>
       </c>
       <c r="B50" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>137291997</v>
       </c>
       <c r="B51" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137292002</v>
       </c>
       <c r="B52" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137313541</v>
       </c>
       <c r="B53" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>137313543</v>
       </c>
       <c r="B54" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137291127</v>
       </c>
       <c r="B55" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>137271130</v>
       </c>
       <c r="B56" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137271169</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>137271173</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>137271174</v>
       </c>
       <c r="B59" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>137271177</v>
       </c>
       <c r="B60" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>137271180</v>
       </c>
       <c r="B61" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>137291995</v>
       </c>
       <c r="B62" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>137313538</v>
       </c>
       <c r="B63" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>137270026</v>
       </c>
       <c r="B64" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>137268905</v>
       </c>
       <c r="B65" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>137270024</v>
       </c>
       <c r="B70" t="n">
-        <v>99742</v>
+        <v>99747</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137271151</v>
       </c>
       <c r="B76" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137271158</v>
       </c>
       <c r="B77" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137273118</v>
       </c>
       <c r="B78" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>137268903</v>
       </c>
       <c r="B80" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>137268906</v>
       </c>
       <c r="B81" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>137268908</v>
       </c>
       <c r="B82" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>137270010</v>
       </c>
       <c r="B83" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>137270029</v>
       </c>
       <c r="B84" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>137270033</v>
       </c>
       <c r="B85" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137271152</v>
       </c>
       <c r="B86" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>137271155</v>
       </c>
       <c r="B87" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>137271156</v>
       </c>
       <c r="B88" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137271161</v>
       </c>
       <c r="B89" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>137271164</v>
       </c>
       <c r="B90" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>137271190</v>
       </c>
       <c r="B91" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>137273111</v>
       </c>
       <c r="B92" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>137287622</v>
       </c>
       <c r="B93" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>137292000</v>
       </c>
       <c r="B94" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>137292001</v>
       </c>
       <c r="B95" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>137313534</v>
       </c>
       <c r="B96" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>137313539</v>
       </c>
       <c r="B97" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137313542</v>
       </c>
       <c r="B98" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>137313544</v>
       </c>
       <c r="B99" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>137268910</v>
       </c>
       <c r="B100" t="n">
-        <v>87322</v>
+        <v>87325</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>137271131</v>
       </c>
       <c r="B101" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>137271132</v>
       </c>
       <c r="B102" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>137271138</v>
       </c>
       <c r="B103" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>137271141</v>
       </c>
       <c r="B104" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>137271144</v>
       </c>
       <c r="B105" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>137271148</v>
       </c>
       <c r="B106" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137271154</v>
       </c>
       <c r="B107" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>137271166</v>
       </c>
       <c r="B108" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>137271167</v>
       </c>
       <c r="B109" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>137271171</v>
       </c>
       <c r="B110" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>137271172</v>
       </c>
       <c r="B111" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>137271178</v>
       </c>
       <c r="B112" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>137271179</v>
       </c>
       <c r="B113" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>137271186</v>
       </c>
       <c r="B114" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>137271187</v>
       </c>
       <c r="B115" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>137273108</v>
       </c>
       <c r="B116" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>137273112</v>
       </c>
       <c r="B117" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>137291062</v>
       </c>
       <c r="B118" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>137291108</v>
       </c>
       <c r="B119" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>137291113</v>
       </c>
       <c r="B120" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>137291120</v>
       </c>
       <c r="B121" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>137312001</v>
       </c>
       <c r="B122" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ131"/>
+  <dimension ref="A1:AZ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2904,7 +2904,7 @@
         <v>137271140</v>
       </c>
       <c r="B22" t="n">
-        <v>93328</v>
+        <v>93330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>137273109</v>
       </c>
       <c r="B24" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137270017</v>
       </c>
       <c r="B25" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137291992</v>
       </c>
       <c r="B26" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>137271130</v>
       </c>
       <c r="B56" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137271169</v>
       </c>
       <c r="B57" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>137271173</v>
       </c>
       <c r="B58" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>137271174</v>
       </c>
       <c r="B59" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>137271177</v>
       </c>
       <c r="B60" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>137271180</v>
       </c>
       <c r="B61" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>137291995</v>
       </c>
       <c r="B62" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>137313538</v>
       </c>
       <c r="B63" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>137270026</v>
       </c>
       <c r="B64" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>137270024</v>
       </c>
       <c r="B70" t="n">
-        <v>99747</v>
+        <v>99750</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137271151</v>
       </c>
       <c r="B76" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137271158</v>
       </c>
       <c r="B77" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137273118</v>
       </c>
       <c r="B78" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -14230,10 +14230,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>97356373</v>
+        <v>137313535</v>
       </c>
       <c r="B123" t="n">
-        <v>87312</v>
+        <v>87573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14241,40 +14241,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>701965</v>
+        <v>701758</v>
       </c>
       <c r="R123" t="n">
-        <v>6359889</v>
+        <v>6359921</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14298,12 +14295,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14319,74 +14326,68 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356373</t>
+          <t>https://artportalen.se/Sighting/137313535</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129317287</v>
+        <v>97356373</v>
       </c>
       <c r="B124" t="n">
-        <v>103385</v>
+        <v>87312</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6037533</v>
+        <v>6037417</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>702037</v>
+        <v>701965</v>
       </c>
       <c r="R124" t="n">
-        <v>6360098</v>
+        <v>6359889</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14410,17 +14411,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14429,35 +14425,31 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317287</t>
+          <t>https://artportalen.se/Sighting/97356373</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129317290</v>
+        <v>129317287</v>
       </c>
       <c r="B125" t="n">
         <v>103385</v>
@@ -14501,10 +14493,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>701998</v>
+        <v>702037</v>
       </c>
       <c r="R125" t="n">
-        <v>6360055</v>
+        <v>6360098</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14572,13 +14564,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317290</t>
+          <t>https://artportalen.se/Sighting/129317287</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129317293</v>
+        <v>129317290</v>
       </c>
       <c r="B126" t="n">
         <v>103385</v>
@@ -14622,10 +14614,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>702001</v>
+        <v>701998</v>
       </c>
       <c r="R126" t="n">
-        <v>6360045</v>
+        <v>6360055</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14662,7 +14654,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>30 cm hög, steil.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14693,13 +14685,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317293</t>
+          <t>https://artportalen.se/Sighting/129317290</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129317303</v>
+        <v>129317293</v>
       </c>
       <c r="B127" t="n">
         <v>103385</v>
@@ -14743,10 +14735,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>701855</v>
+        <v>702001</v>
       </c>
       <c r="R127" t="n">
-        <v>6360068</v>
+        <v>6360045</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14783,7 +14775,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>40 cm hög, steil.</t>
+          <t>30 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14814,13 +14806,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317303</t>
+          <t>https://artportalen.se/Sighting/129317293</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129317304</v>
+        <v>129317303</v>
       </c>
       <c r="B128" t="n">
         <v>103385</v>
@@ -14864,10 +14856,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>701837</v>
+        <v>701855</v>
       </c>
       <c r="R128" t="n">
-        <v>6360008</v>
+        <v>6360068</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14935,13 +14927,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317304</t>
+          <t>https://artportalen.se/Sighting/129317303</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129317307</v>
+        <v>129317304</v>
       </c>
       <c r="B129" t="n">
         <v>103385</v>
@@ -14985,13 +14977,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>701807</v>
+        <v>701837</v>
       </c>
       <c r="R129" t="n">
-        <v>6359985</v>
+        <v>6360008</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15025,7 +15017,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
+          <t>40 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15056,13 +15048,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317307</t>
+          <t>https://artportalen.se/Sighting/129317304</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129317312</v>
+        <v>129317307</v>
       </c>
       <c r="B130" t="n">
         <v>103385</v>
@@ -15106,10 +15098,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>701777</v>
+        <v>701807</v>
       </c>
       <c r="R130" t="n">
-        <v>6360000</v>
+        <v>6359985</v>
       </c>
       <c r="S130" t="n">
         <v>3</v>
@@ -15146,7 +15138,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15177,13 +15169,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317312</t>
+          <t>https://artportalen.se/Sighting/129317307</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129317313</v>
+        <v>129317312</v>
       </c>
       <c r="B131" t="n">
         <v>103385</v>
@@ -15227,10 +15219,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>701778</v>
+        <v>701777</v>
       </c>
       <c r="R131" t="n">
-        <v>6359998</v>
+        <v>6360000</v>
       </c>
       <c r="S131" t="n">
         <v>3</v>
@@ -15267,7 +15259,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>50 cm hög, steil.</t>
+          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15297,6 +15289,127 @@
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317312</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>129317313</v>
+      </c>
+      <c r="B132" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>701778</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6359998</v>
+      </c>
+      <c r="S132" t="n">
+        <v>3</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129317313</t>
         </is>
@@ -15434,6 +15547,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270018</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137291081</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137268911</v>
       </c>
       <c r="B4" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137271128</v>
       </c>
       <c r="B7" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137271133</v>
       </c>
       <c r="B8" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137271135</v>
       </c>
       <c r="B9" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>137271189</v>
       </c>
       <c r="B10" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137313532</v>
       </c>
       <c r="B11" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>137271137</v>
       </c>
       <c r="B12" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137268904</v>
       </c>
       <c r="B13" t="n">
-        <v>90595</v>
+        <v>90600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137291125</v>
       </c>
       <c r="B14" t="n">
-        <v>90595</v>
+        <v>90600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>137270015</v>
       </c>
       <c r="B15" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>137270016</v>
       </c>
       <c r="B16" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>137273122</v>
       </c>
       <c r="B17" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>137273123</v>
       </c>
       <c r="B18" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137291996</v>
       </c>
       <c r="B19" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>137291999</v>
       </c>
       <c r="B20" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>137292003</v>
       </c>
       <c r="B21" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>137271140</v>
       </c>
       <c r="B22" t="n">
-        <v>93330</v>
+        <v>93336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>137273109</v>
       </c>
       <c r="B24" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137270017</v>
       </c>
       <c r="B25" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>137291992</v>
       </c>
       <c r="B26" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>137270012</v>
       </c>
       <c r="B27" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137270023</v>
       </c>
       <c r="B28" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>137270030</v>
       </c>
       <c r="B29" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>137271129</v>
       </c>
       <c r="B30" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>137273117</v>
       </c>
       <c r="B31" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>137273119</v>
       </c>
       <c r="B32" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137291060</v>
       </c>
       <c r="B33" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>137291080</v>
       </c>
       <c r="B34" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137291110</v>
       </c>
       <c r="B35" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>137291117</v>
       </c>
       <c r="B36" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>137291122</v>
       </c>
       <c r="B37" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>137291990</v>
       </c>
       <c r="B38" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>137291991</v>
       </c>
       <c r="B39" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>137291994</v>
       </c>
       <c r="B40" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>137291998</v>
       </c>
       <c r="B41" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>137313537</v>
       </c>
       <c r="B42" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>137313540</v>
       </c>
       <c r="B43" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>137271142</v>
       </c>
       <c r="B44" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>137291124</v>
       </c>
       <c r="B45" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>137270031</v>
       </c>
       <c r="B46" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>137270032</v>
       </c>
       <c r="B47" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>137273120</v>
       </c>
       <c r="B48" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>137287621</v>
       </c>
       <c r="B49" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137291993</v>
       </c>
       <c r="B50" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>137291997</v>
       </c>
       <c r="B51" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137292002</v>
       </c>
       <c r="B52" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137313541</v>
       </c>
       <c r="B53" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>137313543</v>
       </c>
       <c r="B54" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137291127</v>
       </c>
       <c r="B55" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>137271130</v>
       </c>
       <c r="B56" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137271169</v>
       </c>
       <c r="B57" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>137271173</v>
       </c>
       <c r="B58" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>137271174</v>
       </c>
       <c r="B59" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>137271177</v>
       </c>
       <c r="B60" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>137271180</v>
       </c>
       <c r="B61" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>137291995</v>
       </c>
       <c r="B62" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>137313538</v>
       </c>
       <c r="B63" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>137270026</v>
       </c>
       <c r="B64" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>137268905</v>
       </c>
       <c r="B65" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>137270024</v>
       </c>
       <c r="B70" t="n">
-        <v>99750</v>
+        <v>99756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137271151</v>
       </c>
       <c r="B76" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137271158</v>
       </c>
       <c r="B77" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137273118</v>
       </c>
       <c r="B78" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>137268903</v>
       </c>
       <c r="B80" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>137268906</v>
       </c>
       <c r="B81" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>137268908</v>
       </c>
       <c r="B82" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>137270010</v>
       </c>
       <c r="B83" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>137270029</v>
       </c>
       <c r="B84" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>137270033</v>
       </c>
       <c r="B85" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137271152</v>
       </c>
       <c r="B86" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>137271155</v>
       </c>
       <c r="B87" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>137271156</v>
       </c>
       <c r="B88" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137271161</v>
       </c>
       <c r="B89" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>137271164</v>
       </c>
       <c r="B90" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>137271190</v>
       </c>
       <c r="B91" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>137273111</v>
       </c>
       <c r="B92" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>137287622</v>
       </c>
       <c r="B93" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>137292000</v>
       </c>
       <c r="B94" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>137292001</v>
       </c>
       <c r="B95" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>137313534</v>
       </c>
       <c r="B96" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>137313539</v>
       </c>
       <c r="B97" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137313542</v>
       </c>
       <c r="B98" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>137313544</v>
       </c>
       <c r="B99" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>137268910</v>
       </c>
       <c r="B100" t="n">
-        <v>87325</v>
+        <v>87330</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>137271131</v>
       </c>
       <c r="B101" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>137271132</v>
       </c>
       <c r="B102" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>137271138</v>
       </c>
       <c r="B103" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>137271141</v>
       </c>
       <c r="B104" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>137271144</v>
       </c>
       <c r="B105" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>137271148</v>
       </c>
       <c r="B106" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137271154</v>
       </c>
       <c r="B107" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>137271166</v>
       </c>
       <c r="B108" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>137271167</v>
       </c>
       <c r="B109" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>137271171</v>
       </c>
       <c r="B110" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>137271172</v>
       </c>
       <c r="B111" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>137271178</v>
       </c>
       <c r="B112" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>137271179</v>
       </c>
       <c r="B113" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>137271186</v>
       </c>
       <c r="B114" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>137271187</v>
       </c>
       <c r="B115" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>137273108</v>
       </c>
       <c r="B116" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>137273112</v>
       </c>
       <c r="B117" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>137291062</v>
       </c>
       <c r="B118" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>137291108</v>
       </c>
       <c r="B119" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>137291113</v>
       </c>
       <c r="B120" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>137291120</v>
       </c>
       <c r="B121" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>137312001</v>
       </c>
       <c r="B122" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>137313535</v>
       </c>
       <c r="B123" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270018</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137291081</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137268911</v>
       </c>
       <c r="B4" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137271128</v>
       </c>
       <c r="B7" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137271133</v>
       </c>
       <c r="B8" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137271135</v>
       </c>
       <c r="B9" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>137271189</v>
       </c>
       <c r="B10" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137313532</v>
       </c>
       <c r="B11" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>137417411</v>
       </c>
       <c r="B12" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137417414</v>
       </c>
       <c r="B13" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>137271137</v>
       </c>
       <c r="B14" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>137268904</v>
       </c>
       <c r="B15" t="n">
-        <v>90600</v>
+        <v>90611</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>137291125</v>
       </c>
       <c r="B16" t="n">
-        <v>90600</v>
+        <v>90611</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>137270015</v>
       </c>
       <c r="B17" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>137270016</v>
       </c>
       <c r="B18" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137273122</v>
       </c>
       <c r="B19" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>137273123</v>
       </c>
       <c r="B20" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>137291996</v>
       </c>
       <c r="B21" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>137291999</v>
       </c>
       <c r="B22" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>137292003</v>
       </c>
       <c r="B23" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>137417425</v>
       </c>
       <c r="B24" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137271140</v>
       </c>
       <c r="B25" t="n">
-        <v>93336</v>
+        <v>93348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>137273109</v>
       </c>
       <c r="B27" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137270017</v>
       </c>
       <c r="B28" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>137291992</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>137270012</v>
       </c>
       <c r="B30" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>137270023</v>
       </c>
       <c r="B31" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>137270030</v>
       </c>
       <c r="B32" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137271129</v>
       </c>
       <c r="B33" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>137273117</v>
       </c>
       <c r="B34" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>137273119</v>
       </c>
       <c r="B35" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>137291060</v>
       </c>
       <c r="B36" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>137291080</v>
       </c>
       <c r="B37" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>137291110</v>
       </c>
       <c r="B38" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>137291117</v>
       </c>
       <c r="B39" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>137291122</v>
       </c>
       <c r="B40" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>137291990</v>
       </c>
       <c r="B41" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>137291991</v>
       </c>
       <c r="B42" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>137291994</v>
       </c>
       <c r="B43" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>137291998</v>
       </c>
       <c r="B44" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>137313537</v>
       </c>
       <c r="B45" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137313540</v>
       </c>
       <c r="B46" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>137417427</v>
       </c>
       <c r="B47" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>137417446</v>
       </c>
       <c r="B48" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>137271142</v>
       </c>
       <c r="B49" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>137291124</v>
       </c>
       <c r="B50" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>137417459</v>
       </c>
       <c r="B51" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137270031</v>
       </c>
       <c r="B52" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137270032</v>
       </c>
       <c r="B53" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>137273120</v>
       </c>
       <c r="B54" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137287621</v>
       </c>
       <c r="B55" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>137291993</v>
       </c>
       <c r="B56" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>137291997</v>
       </c>
       <c r="B57" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>137292002</v>
       </c>
       <c r="B58" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>137313541</v>
       </c>
       <c r="B59" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>137313543</v>
       </c>
       <c r="B60" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>137417402</v>
       </c>
       <c r="B61" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>137417429</v>
       </c>
       <c r="B62" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>137417445</v>
       </c>
       <c r="B63" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>137291127</v>
       </c>
       <c r="B64" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>137417403</v>
       </c>
       <c r="B65" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>137417453</v>
       </c>
       <c r="B66" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>137417454</v>
       </c>
       <c r="B67" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>137271130</v>
       </c>
       <c r="B68" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>137271169</v>
       </c>
       <c r="B69" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>137271173</v>
       </c>
       <c r="B70" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>137271174</v>
       </c>
       <c r="B71" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>137271177</v>
       </c>
       <c r="B72" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>137271180</v>
       </c>
       <c r="B73" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>137291995</v>
       </c>
       <c r="B74" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>137313538</v>
       </c>
       <c r="B75" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>137417416</v>
       </c>
       <c r="B76" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137417991</v>
       </c>
       <c r="B77" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>137418020</v>
       </c>
       <c r="B78" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>137417415</v>
       </c>
       <c r="B79" t="n">
-        <v>89321</v>
+        <v>89332</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>137270026</v>
       </c>
       <c r="B80" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>137417439</v>
       </c>
       <c r="B81" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>137417455</v>
       </c>
       <c r="B82" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>137417456</v>
       </c>
       <c r="B83" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>137417433</v>
       </c>
       <c r="B84" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137418034</v>
       </c>
       <c r="B85" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>137270024</v>
       </c>
       <c r="B104" t="n">
-        <v>99756</v>
+        <v>99768</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137271151</v>
       </c>
       <c r="B110" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137271158</v>
       </c>
       <c r="B111" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137273118</v>
       </c>
       <c r="B112" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137417995</v>
       </c>
       <c r="B113" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>137418044</v>
       </c>
       <c r="B114" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>137268903</v>
       </c>
       <c r="B116" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137268906</v>
       </c>
       <c r="B117" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>137268908</v>
       </c>
       <c r="B118" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>137270010</v>
       </c>
       <c r="B119" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>137270029</v>
       </c>
       <c r="B120" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>137270033</v>
       </c>
       <c r="B121" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>137271152</v>
       </c>
       <c r="B122" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>137271155</v>
       </c>
       <c r="B123" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>137271156</v>
       </c>
       <c r="B124" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>137271161</v>
       </c>
       <c r="B125" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>137271164</v>
       </c>
       <c r="B126" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>137271190</v>
       </c>
       <c r="B127" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>137273111</v>
       </c>
       <c r="B128" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>137287622</v>
       </c>
       <c r="B129" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>137292000</v>
       </c>
       <c r="B130" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>137292001</v>
       </c>
       <c r="B131" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>137313534</v>
       </c>
       <c r="B132" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>137313539</v>
       </c>
       <c r="B133" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>137313542</v>
       </c>
       <c r="B134" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>137313544</v>
       </c>
       <c r="B135" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>137417406</v>
       </c>
       <c r="B136" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>137417421</v>
       </c>
       <c r="B137" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>137417436</v>
       </c>
       <c r="B138" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137417438</v>
       </c>
       <c r="B139" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>137417404</v>
       </c>
       <c r="B140" t="n">
-        <v>87650</v>
+        <v>87661</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>137417431</v>
       </c>
       <c r="B141" t="n">
-        <v>87650</v>
+        <v>87661</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>137268910</v>
       </c>
       <c r="B142" t="n">
-        <v>87330</v>
+        <v>87341</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>137271131</v>
       </c>
       <c r="B143" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>137271132</v>
       </c>
       <c r="B144" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>137271138</v>
       </c>
       <c r="B145" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>137271141</v>
       </c>
       <c r="B146" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>137271144</v>
       </c>
       <c r="B147" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>137271148</v>
       </c>
       <c r="B148" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>137271154</v>
       </c>
       <c r="B149" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>137271166</v>
       </c>
       <c r="B150" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>137271167</v>
       </c>
       <c r="B151" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>137271171</v>
       </c>
       <c r="B152" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>137271172</v>
       </c>
       <c r="B153" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>137271178</v>
       </c>
       <c r="B154" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>137271179</v>
       </c>
       <c r="B155" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>137271186</v>
       </c>
       <c r="B156" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>137271187</v>
       </c>
       <c r="B157" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>137273108</v>
       </c>
       <c r="B158" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>137273112</v>
       </c>
       <c r="B159" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>137291062</v>
       </c>
       <c r="B160" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>137291108</v>
       </c>
       <c r="B161" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>137291113</v>
       </c>
       <c r="B162" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>137291120</v>
       </c>
       <c r="B163" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>137312001</v>
       </c>
       <c r="B164" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>137313535</v>
       </c>
       <c r="B165" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>137417398</v>
       </c>
       <c r="B166" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>137417401</v>
       </c>
       <c r="B167" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>137417417</v>
       </c>
       <c r="B168" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>137417423</v>
       </c>
       <c r="B169" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>137417424</v>
       </c>
       <c r="B170" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>137417428</v>
       </c>
       <c r="B171" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>137417458</v>
       </c>
       <c r="B172" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>137417408</v>
       </c>
       <c r="B182" t="n">
-        <v>87606</v>
+        <v>87617</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>137417419</v>
       </c>
       <c r="B183" t="n">
-        <v>87606</v>
+        <v>87617</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>137417422</v>
       </c>
       <c r="B184" t="n">
-        <v>87606</v>
+        <v>87617</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>137417443</v>
       </c>
       <c r="B185" t="n">
-        <v>87606</v>
+        <v>87617</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270018</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137291081</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137268911</v>
       </c>
       <c r="B4" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137271128</v>
       </c>
       <c r="B7" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137271133</v>
       </c>
       <c r="B8" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137271135</v>
       </c>
       <c r="B9" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>137271189</v>
       </c>
       <c r="B10" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137313532</v>
       </c>
       <c r="B11" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>137417411</v>
       </c>
       <c r="B12" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137417414</v>
       </c>
       <c r="B13" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>137271137</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>137268904</v>
       </c>
       <c r="B15" t="n">
-        <v>90611</v>
+        <v>90612</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>137291125</v>
       </c>
       <c r="B16" t="n">
-        <v>90611</v>
+        <v>90612</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>137270015</v>
       </c>
       <c r="B17" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>137270016</v>
       </c>
       <c r="B18" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137273122</v>
       </c>
       <c r="B19" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>137273123</v>
       </c>
       <c r="B20" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>137291996</v>
       </c>
       <c r="B21" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>137291999</v>
       </c>
       <c r="B22" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>137292003</v>
       </c>
       <c r="B23" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>137417425</v>
       </c>
       <c r="B24" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137271140</v>
       </c>
       <c r="B25" t="n">
-        <v>93348</v>
+        <v>93349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>137273109</v>
       </c>
       <c r="B27" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137270017</v>
       </c>
       <c r="B28" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>137291992</v>
       </c>
       <c r="B29" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>137270012</v>
       </c>
       <c r="B30" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>137270023</v>
       </c>
       <c r="B31" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>137270030</v>
       </c>
       <c r="B32" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137271129</v>
       </c>
       <c r="B33" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>137273117</v>
       </c>
       <c r="B34" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>137273119</v>
       </c>
       <c r="B35" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>137291060</v>
       </c>
       <c r="B36" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>137291080</v>
       </c>
       <c r="B37" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>137291110</v>
       </c>
       <c r="B38" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>137291117</v>
       </c>
       <c r="B39" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>137291122</v>
       </c>
       <c r="B40" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>137291990</v>
       </c>
       <c r="B41" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>137291991</v>
       </c>
       <c r="B42" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>137291994</v>
       </c>
       <c r="B43" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>137291998</v>
       </c>
       <c r="B44" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>137313537</v>
       </c>
       <c r="B45" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137313540</v>
       </c>
       <c r="B46" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>137417427</v>
       </c>
       <c r="B47" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>137417446</v>
       </c>
       <c r="B48" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>137271142</v>
       </c>
       <c r="B49" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>137291124</v>
       </c>
       <c r="B50" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>137417459</v>
       </c>
       <c r="B51" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137270031</v>
       </c>
       <c r="B52" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137270032</v>
       </c>
       <c r="B53" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>137273120</v>
       </c>
       <c r="B54" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137287621</v>
       </c>
       <c r="B55" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>137291993</v>
       </c>
       <c r="B56" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>137291997</v>
       </c>
       <c r="B57" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>137292002</v>
       </c>
       <c r="B58" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>137313541</v>
       </c>
       <c r="B59" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>137313543</v>
       </c>
       <c r="B60" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>137417402</v>
       </c>
       <c r="B61" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>137417429</v>
       </c>
       <c r="B62" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>137417445</v>
       </c>
       <c r="B63" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>137291127</v>
       </c>
       <c r="B64" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>137417403</v>
       </c>
       <c r="B65" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>137417453</v>
       </c>
       <c r="B66" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>137417454</v>
       </c>
       <c r="B67" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>137271130</v>
       </c>
       <c r="B68" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>137271169</v>
       </c>
       <c r="B69" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>137271173</v>
       </c>
       <c r="B70" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>137271174</v>
       </c>
       <c r="B71" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>137271177</v>
       </c>
       <c r="B72" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>137271180</v>
       </c>
       <c r="B73" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>137291995</v>
       </c>
       <c r="B74" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>137313538</v>
       </c>
       <c r="B75" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>137417416</v>
       </c>
       <c r="B76" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137417991</v>
       </c>
       <c r="B77" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>137418020</v>
       </c>
       <c r="B78" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>137417415</v>
       </c>
       <c r="B79" t="n">
-        <v>89332</v>
+        <v>89333</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>137270026</v>
       </c>
       <c r="B80" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>137417439</v>
       </c>
       <c r="B81" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>137417455</v>
       </c>
       <c r="B82" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>137417456</v>
       </c>
       <c r="B83" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>137270024</v>
       </c>
       <c r="B104" t="n">
-        <v>99768</v>
+        <v>99769</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137271151</v>
       </c>
       <c r="B110" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137271158</v>
       </c>
       <c r="B111" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137273118</v>
       </c>
       <c r="B112" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137417995</v>
       </c>
       <c r="B113" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>137418044</v>
       </c>
       <c r="B114" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>137268903</v>
       </c>
       <c r="B116" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137268906</v>
       </c>
       <c r="B117" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>137268908</v>
       </c>
       <c r="B118" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>137270010</v>
       </c>
       <c r="B119" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>137270029</v>
       </c>
       <c r="B120" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>137270033</v>
       </c>
       <c r="B121" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>137271152</v>
       </c>
       <c r="B122" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>137271155</v>
       </c>
       <c r="B123" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>137271156</v>
       </c>
       <c r="B124" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>137271161</v>
       </c>
       <c r="B125" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>137271164</v>
       </c>
       <c r="B126" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>137271190</v>
       </c>
       <c r="B127" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>137273111</v>
       </c>
       <c r="B128" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>137287622</v>
       </c>
       <c r="B129" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>137292000</v>
       </c>
       <c r="B130" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>137292001</v>
       </c>
       <c r="B131" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>137313534</v>
       </c>
       <c r="B132" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>137313539</v>
       </c>
       <c r="B133" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>137313542</v>
       </c>
       <c r="B134" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>137313544</v>
       </c>
       <c r="B135" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>137417406</v>
       </c>
       <c r="B136" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>137417421</v>
       </c>
       <c r="B137" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>137417436</v>
       </c>
       <c r="B138" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137417438</v>
       </c>
       <c r="B139" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>137417404</v>
       </c>
       <c r="B140" t="n">
-        <v>87661</v>
+        <v>87662</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>137417431</v>
       </c>
       <c r="B141" t="n">
-        <v>87661</v>
+        <v>87662</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>137268910</v>
       </c>
       <c r="B142" t="n">
-        <v>87341</v>
+        <v>87342</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>137271131</v>
       </c>
       <c r="B143" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>137271132</v>
       </c>
       <c r="B144" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>137271138</v>
       </c>
       <c r="B145" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>137271141</v>
       </c>
       <c r="B146" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>137271144</v>
       </c>
       <c r="B147" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>137271148</v>
       </c>
       <c r="B148" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>137271154</v>
       </c>
       <c r="B149" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>137271166</v>
       </c>
       <c r="B150" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>137271167</v>
       </c>
       <c r="B151" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>137271171</v>
       </c>
       <c r="B152" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>137271172</v>
       </c>
       <c r="B153" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>137271178</v>
       </c>
       <c r="B154" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>137271179</v>
       </c>
       <c r="B155" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>137271186</v>
       </c>
       <c r="B156" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>137271187</v>
       </c>
       <c r="B157" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>137273108</v>
       </c>
       <c r="B158" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>137273112</v>
       </c>
       <c r="B159" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>137291062</v>
       </c>
       <c r="B160" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>137291108</v>
       </c>
       <c r="B161" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>137291113</v>
       </c>
       <c r="B162" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>137291120</v>
       </c>
       <c r="B163" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>137312001</v>
       </c>
       <c r="B164" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>137313535</v>
       </c>
       <c r="B165" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>137417398</v>
       </c>
       <c r="B166" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>137417401</v>
       </c>
       <c r="B167" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>137417417</v>
       </c>
       <c r="B168" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>137417423</v>
       </c>
       <c r="B169" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>137417424</v>
       </c>
       <c r="B170" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>137417428</v>
       </c>
       <c r="B171" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>137417458</v>
       </c>
       <c r="B172" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>137417408</v>
       </c>
       <c r="B182" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>137417419</v>
       </c>
       <c r="B183" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>137417422</v>
       </c>
       <c r="B184" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>137417443</v>
       </c>
       <c r="B185" t="n">
-        <v>87617</v>
+        <v>87618</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270018</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137291081</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137268911</v>
       </c>
       <c r="B4" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137271128</v>
       </c>
       <c r="B7" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137271133</v>
       </c>
       <c r="B8" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137271135</v>
       </c>
       <c r="B9" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>137271189</v>
       </c>
       <c r="B10" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>137313532</v>
       </c>
       <c r="B11" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>137417411</v>
       </c>
       <c r="B12" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137417414</v>
       </c>
       <c r="B13" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>137271137</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>137268904</v>
       </c>
       <c r="B15" t="n">
-        <v>90612</v>
+        <v>90615</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>137291125</v>
       </c>
       <c r="B16" t="n">
-        <v>90612</v>
+        <v>90615</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>137270015</v>
       </c>
       <c r="B17" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>137270016</v>
       </c>
       <c r="B18" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137273122</v>
       </c>
       <c r="B19" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>137273123</v>
       </c>
       <c r="B20" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>137291996</v>
       </c>
       <c r="B21" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>137291999</v>
       </c>
       <c r="B22" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>137292003</v>
       </c>
       <c r="B23" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>137417425</v>
       </c>
       <c r="B24" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137271140</v>
       </c>
       <c r="B25" t="n">
-        <v>93349</v>
+        <v>93352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>137273109</v>
       </c>
       <c r="B27" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137270017</v>
       </c>
       <c r="B28" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>137291992</v>
       </c>
       <c r="B29" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>137270012</v>
       </c>
       <c r="B30" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>137270023</v>
       </c>
       <c r="B31" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>137270030</v>
       </c>
       <c r="B32" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>137271129</v>
       </c>
       <c r="B33" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>137273117</v>
       </c>
       <c r="B34" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>137273119</v>
       </c>
       <c r="B35" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>137291060</v>
       </c>
       <c r="B36" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>137291080</v>
       </c>
       <c r="B37" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>137291110</v>
       </c>
       <c r="B38" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>137291117</v>
       </c>
       <c r="B39" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>137291122</v>
       </c>
       <c r="B40" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>137291990</v>
       </c>
       <c r="B41" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>137291991</v>
       </c>
       <c r="B42" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>137291994</v>
       </c>
       <c r="B43" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>137291998</v>
       </c>
       <c r="B44" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>137313537</v>
       </c>
       <c r="B45" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>137313540</v>
       </c>
       <c r="B46" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>137417427</v>
       </c>
       <c r="B47" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>137417446</v>
       </c>
       <c r="B48" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>137271142</v>
       </c>
       <c r="B49" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>137291124</v>
       </c>
       <c r="B50" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>137417459</v>
       </c>
       <c r="B51" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137270031</v>
       </c>
       <c r="B52" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137270032</v>
       </c>
       <c r="B53" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>137273120</v>
       </c>
       <c r="B54" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137287621</v>
       </c>
       <c r="B55" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>137291993</v>
       </c>
       <c r="B56" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>137291997</v>
       </c>
       <c r="B57" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>137292002</v>
       </c>
       <c r="B58" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>137313541</v>
       </c>
       <c r="B59" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>137313543</v>
       </c>
       <c r="B60" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>137417402</v>
       </c>
       <c r="B61" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>137417429</v>
       </c>
       <c r="B62" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>137417445</v>
       </c>
       <c r="B63" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>137291127</v>
       </c>
       <c r="B64" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>137417403</v>
       </c>
       <c r="B65" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>137417453</v>
       </c>
       <c r="B66" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>137417454</v>
       </c>
       <c r="B67" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>137271130</v>
       </c>
       <c r="B68" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>137271169</v>
       </c>
       <c r="B69" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>137271173</v>
       </c>
       <c r="B70" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>137271174</v>
       </c>
       <c r="B71" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>137271177</v>
       </c>
       <c r="B72" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>137271180</v>
       </c>
       <c r="B73" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>137291995</v>
       </c>
       <c r="B74" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>137313538</v>
       </c>
       <c r="B75" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>137417416</v>
       </c>
       <c r="B76" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137417991</v>
       </c>
       <c r="B77" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>137418020</v>
       </c>
       <c r="B78" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>137417415</v>
       </c>
       <c r="B79" t="n">
-        <v>89333</v>
+        <v>89336</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>137270026</v>
       </c>
       <c r="B80" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>137417439</v>
       </c>
       <c r="B81" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>137417455</v>
       </c>
       <c r="B82" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>137417456</v>
       </c>
       <c r="B83" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>137270024</v>
       </c>
       <c r="B104" t="n">
-        <v>99769</v>
+        <v>99772</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137271151</v>
       </c>
       <c r="B110" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137271158</v>
       </c>
       <c r="B111" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137273118</v>
       </c>
       <c r="B112" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137417995</v>
       </c>
       <c r="B113" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>137418044</v>
       </c>
       <c r="B114" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>137268903</v>
       </c>
       <c r="B116" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137268906</v>
       </c>
       <c r="B117" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>137268908</v>
       </c>
       <c r="B118" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>137270010</v>
       </c>
       <c r="B119" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>137270029</v>
       </c>
       <c r="B120" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>137270033</v>
       </c>
       <c r="B121" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>137271152</v>
       </c>
       <c r="B122" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>137271155</v>
       </c>
       <c r="B123" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>137271156</v>
       </c>
       <c r="B124" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>137271161</v>
       </c>
       <c r="B125" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>137271164</v>
       </c>
       <c r="B126" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>137271190</v>
       </c>
       <c r="B127" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>137273111</v>
       </c>
       <c r="B128" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>137287622</v>
       </c>
       <c r="B129" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>137292000</v>
       </c>
       <c r="B130" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>137292001</v>
       </c>
       <c r="B131" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>137313534</v>
       </c>
       <c r="B132" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>137313539</v>
       </c>
       <c r="B133" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>137313542</v>
       </c>
       <c r="B134" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>137313544</v>
       </c>
       <c r="B135" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>137417406</v>
       </c>
       <c r="B136" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>137417421</v>
       </c>
       <c r="B137" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>137417436</v>
       </c>
       <c r="B138" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137417438</v>
       </c>
       <c r="B139" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>137417404</v>
       </c>
       <c r="B140" t="n">
-        <v>87662</v>
+        <v>87665</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>137417431</v>
       </c>
       <c r="B141" t="n">
-        <v>87662</v>
+        <v>87665</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>137268910</v>
       </c>
       <c r="B142" t="n">
-        <v>87342</v>
+        <v>87345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>137271131</v>
       </c>
       <c r="B143" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>137271132</v>
       </c>
       <c r="B144" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>137271138</v>
       </c>
       <c r="B145" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>137271141</v>
       </c>
       <c r="B146" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>137271144</v>
       </c>
       <c r="B147" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>137271148</v>
       </c>
       <c r="B148" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>137271154</v>
       </c>
       <c r="B149" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>137271166</v>
       </c>
       <c r="B150" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>137271167</v>
       </c>
       <c r="B151" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>137271171</v>
       </c>
       <c r="B152" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>137271172</v>
       </c>
       <c r="B153" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>137271178</v>
       </c>
       <c r="B154" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>137271179</v>
       </c>
       <c r="B155" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>137271186</v>
       </c>
       <c r="B156" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>137271187</v>
       </c>
       <c r="B157" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>137273108</v>
       </c>
       <c r="B158" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>137273112</v>
       </c>
       <c r="B159" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>137291062</v>
       </c>
       <c r="B160" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>137291108</v>
       </c>
       <c r="B161" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>137291113</v>
       </c>
       <c r="B162" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>137291120</v>
       </c>
       <c r="B163" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>137312001</v>
       </c>
       <c r="B164" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>137313535</v>
       </c>
       <c r="B165" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>137417398</v>
       </c>
       <c r="B166" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>137417401</v>
       </c>
       <c r="B167" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>137417417</v>
       </c>
       <c r="B168" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>137417423</v>
       </c>
       <c r="B169" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>137417424</v>
       </c>
       <c r="B170" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>137417428</v>
       </c>
       <c r="B171" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>137417458</v>
       </c>
       <c r="B172" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>137417408</v>
       </c>
       <c r="B182" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>137417419</v>
       </c>
       <c r="B183" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>137417422</v>
       </c>
       <c r="B184" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>137417443</v>
       </c>
       <c r="B185" t="n">
-        <v>87618</v>
+        <v>87621</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ185"/>
+  <dimension ref="A1:AZ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9283,7 +9283,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137417415</v>
+        <v>137270011</v>
       </c>
       <c r="B79" t="n">
         <v>89336</v>
@@ -9314,17 +9314,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>701911</v>
+        <v>701706</v>
       </c>
       <c r="R79" t="n">
-        <v>6360111</v>
+        <v>6360223</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9348,22 +9348,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9372,33 +9372,34 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417415</t>
+          <t>https://artportalen.se/Sighting/137270011</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>137270026</v>
+        <v>137417415</v>
       </c>
       <c r="B80" t="n">
-        <v>93156</v>
+        <v>89336</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9406,37 +9407,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>4379</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>702082</v>
+        <v>701911</v>
       </c>
       <c r="R80" t="n">
-        <v>6360090</v>
+        <v>6360111</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9460,22 +9461,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9490,62 +9491,62 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270026</t>
+          <t>https://artportalen.se/Sighting/137417415</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>137417439</v>
+        <v>137270026</v>
       </c>
       <c r="B81" t="n">
-        <v>91692</v>
+        <v>93156</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>702154</v>
+        <v>702082</v>
       </c>
       <c r="R81" t="n">
-        <v>6360290</v>
+        <v>6360090</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9572,27 +9573,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Närmsta gran 25 meter bort</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9607,24 +9603,24 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417439</t>
+          <t>https://artportalen.se/Sighting/137270026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137417455</v>
+        <v>137417439</v>
       </c>
       <c r="B82" t="n">
         <v>91692</v>
@@ -9659,13 +9655,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>702055</v>
+        <v>702154</v>
       </c>
       <c r="R82" t="n">
-        <v>6360121</v>
+        <v>6360290</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9694,7 +9690,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9704,7 +9700,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Närmsta gran 25 meter bort</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9730,13 +9731,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417455</t>
+          <t>https://artportalen.se/Sighting/137417439</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>137417456</v>
+        <v>137417455</v>
       </c>
       <c r="B83" t="n">
         <v>91692</v>
@@ -9771,13 +9772,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>702029</v>
+        <v>702055</v>
       </c>
       <c r="R83" t="n">
-        <v>6360071</v>
+        <v>6360121</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9806,7 +9807,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9816,7 +9817,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9842,38 +9843,38 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417456</t>
+          <t>https://artportalen.se/Sighting/137417455</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>137417433</v>
+        <v>137417456</v>
       </c>
       <c r="B84" t="n">
-        <v>75610</v>
+        <v>91692</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6426</v>
+        <v>5747</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9883,13 +9884,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>701999</v>
+        <v>702029</v>
       </c>
       <c r="R84" t="n">
-        <v>6360344</v>
+        <v>6360071</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9918,7 +9919,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9928,7 +9929,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9954,13 +9955,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417433</t>
+          <t>https://artportalen.se/Sighting/137417456</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>137418034</v>
+        <v>137417433</v>
       </c>
       <c r="B85" t="n">
         <v>75610</v>
@@ -9989,22 +9990,19 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lojsta-Bjärs, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>702228</v>
+        <v>701999</v>
       </c>
       <c r="R85" t="n">
-        <v>6360214</v>
+        <v>6360344</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10031,45 +10029,54 @@
           <t>2026-10-23</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137418034</t>
+          <t>https://artportalen.se/Sighting/137417433</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>137417440</v>
+        <v>137418034</v>
       </c>
       <c r="B86" t="n">
-        <v>57956</v>
+        <v>75610</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10077,41 +10084,40 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100001</v>
+        <v>6426</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta-Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>702163</v>
+        <v>702228</v>
       </c>
       <c r="R86" t="n">
-        <v>6360282</v>
+        <v>6360214</v>
       </c>
       <c r="S86" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10138,71 +10144,62 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417440</t>
+          <t>https://artportalen.se/Sighting/137418034</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>137268905</v>
+        <v>137417440</v>
       </c>
       <c r="B87" t="n">
-        <v>58032</v>
+        <v>57956</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10211,19 +10208,23 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>702009</v>
+        <v>702163</v>
       </c>
       <c r="R87" t="n">
-        <v>6360293</v>
+        <v>6360282</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10247,22 +10248,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10277,24 +10278,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268905</t>
+          <t>https://artportalen.se/Sighting/137417440</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>137417434</v>
+        <v>137268905</v>
       </c>
       <c r="B88" t="n">
         <v>58032</v>
@@ -10323,23 +10324,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701934</v>
+        <v>702009</v>
       </c>
       <c r="R88" t="n">
-        <v>6360325</v>
+        <v>6360293</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10363,22 +10360,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10393,24 +10390,24 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417434</t>
+          <t>https://artportalen.se/Sighting/137268905</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137417435</v>
+        <v>137417434</v>
       </c>
       <c r="B89" t="n">
         <v>58032</v>
@@ -10449,13 +10446,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>702054</v>
+        <v>701934</v>
       </c>
       <c r="R89" t="n">
-        <v>6360294</v>
+        <v>6360325</v>
       </c>
       <c r="S89" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10484,7 +10481,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10494,7 +10491,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10520,13 +10517,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417435</t>
+          <t>https://artportalen.se/Sighting/137417434</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>137417437</v>
+        <v>137417435</v>
       </c>
       <c r="B90" t="n">
         <v>58032</v>
@@ -10565,13 +10562,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>702058</v>
+        <v>702054</v>
       </c>
       <c r="R90" t="n">
-        <v>6360291</v>
+        <v>6360294</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10600,7 +10597,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10610,12 +10607,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska födospår.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10641,13 +10633,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417437</t>
+          <t>https://artportalen.se/Sighting/137417435</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>137417452</v>
+        <v>137417437</v>
       </c>
       <c r="B91" t="n">
         <v>58032</v>
@@ -10686,10 +10678,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>702092</v>
+        <v>702058</v>
       </c>
       <c r="R91" t="n">
-        <v>6360149</v>
+        <v>6360291</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10721,7 +10713,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10731,7 +10723,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska födospår.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10757,13 +10754,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417452</t>
+          <t>https://artportalen.se/Sighting/137417437</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>137417457</v>
+        <v>137417452</v>
       </c>
       <c r="B92" t="n">
         <v>58032</v>
@@ -10802,13 +10799,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>701967</v>
+        <v>702092</v>
       </c>
       <c r="R92" t="n">
-        <v>6360008</v>
+        <v>6360149</v>
       </c>
       <c r="S92" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10837,7 +10834,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10847,7 +10844,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10873,13 +10870,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417457</t>
+          <t>https://artportalen.se/Sighting/137417452</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>137417460</v>
+        <v>137417457</v>
       </c>
       <c r="B93" t="n">
         <v>58032</v>
@@ -10918,13 +10915,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>701777</v>
+        <v>701967</v>
       </c>
       <c r="R93" t="n">
-        <v>6359993</v>
+        <v>6360008</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10953,7 +10950,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10963,7 +10960,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10989,13 +10986,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417460</t>
+          <t>https://artportalen.se/Sighting/137417457</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>137418011</v>
+        <v>137417460</v>
       </c>
       <c r="B94" t="n">
         <v>58032</v>
@@ -11030,17 +11027,17 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lojsta-Bjärs, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>701996</v>
+        <v>701777</v>
       </c>
       <c r="R94" t="n">
-        <v>6360275</v>
+        <v>6359993</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11067,9 +11064,19 @@
           <t>2026-10-23</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11084,24 +11091,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137418011</t>
+          <t>https://artportalen.se/Sighting/137417460</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>137418041</v>
+        <v>137418011</v>
       </c>
       <c r="B95" t="n">
         <v>58032</v>
@@ -11140,10 +11147,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>702288</v>
+        <v>701996</v>
       </c>
       <c r="R95" t="n">
-        <v>6360238</v>
+        <v>6360275</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11201,16 +11208,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137418041</t>
+          <t>https://artportalen.se/Sighting/137418011</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137418037</v>
+        <v>137418041</v>
       </c>
       <c r="B96" t="n">
-        <v>4783</v>
+        <v>58032</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11218,25 +11225,24 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
@@ -11247,10 +11253,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>702228</v>
+        <v>702288</v>
       </c>
       <c r="R96" t="n">
-        <v>6360214</v>
+        <v>6360238</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11291,7 +11297,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11309,16 +11314,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137418037</t>
+          <t>https://artportalen.se/Sighting/137418041</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137418040</v>
+        <v>137418037</v>
       </c>
       <c r="B97" t="n">
-        <v>5188</v>
+        <v>4783</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11326,21 +11331,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11417,73 +11422,59 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137418040</t>
+          <t>https://artportalen.se/Sighting/137418037</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129317244</v>
+        <v>137418040</v>
       </c>
       <c r="B98" t="n">
-        <v>43467</v>
+        <v>5188</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>101242</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta-Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>702020</v>
+        <v>702228</v>
       </c>
       <c r="R98" t="n">
-        <v>6360085</v>
+        <v>6360214</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11507,12 +11498,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11521,38 +11512,34 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, glänta.</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317244</t>
+          <t>https://artportalen.se/Sighting/137418040</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137418042</v>
+        <v>129317244</v>
       </c>
       <c r="B99" t="n">
-        <v>5504</v>
+        <v>43467</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11560,42 +11547,56 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>101410</v>
+        <v>101242</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lojsta-Bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>702288</v>
+        <v>702020</v>
       </c>
       <c r="R99" t="n">
-        <v>6360238</v>
+        <v>6360085</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11619,12 +11620,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11633,34 +11634,38 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137418042</t>
+          <t>https://artportalen.se/Sighting/129317244</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137417447</v>
+        <v>137418042</v>
       </c>
       <c r="B100" t="n">
-        <v>57445</v>
+        <v>5504</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11668,41 +11673,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102954</v>
+        <v>101410</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta-Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>702331</v>
+        <v>702288</v>
       </c>
       <c r="R100" t="n">
-        <v>6360252</v>
+        <v>6360238</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11729,71 +11735,62 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417447</t>
+          <t>https://artportalen.se/Sighting/137418042</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>97357029</v>
+        <v>137417447</v>
       </c>
       <c r="B101" t="n">
-        <v>5199</v>
+        <v>57445</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>102954</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11802,24 +11799,23 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>701735</v>
+        <v>702331</v>
       </c>
       <c r="R101" t="n">
-        <v>6360028</v>
+        <v>6360252</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11843,12 +11839,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11857,34 +11863,33 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97357029</t>
+          <t>https://artportalen.se/Sighting/137417447</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129317281</v>
+        <v>97357029</v>
       </c>
       <c r="B102" t="n">
-        <v>99147</v>
+        <v>5199</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11892,46 +11897,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219864</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>701848</v>
+        <v>701735</v>
       </c>
       <c r="R102" t="n">
-        <v>6360188</v>
+        <v>6360028</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11955,12 +11956,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11969,35 +11970,31 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317281</t>
+          <t>https://artportalen.se/Sighting/97357029</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129317294</v>
+        <v>129317281</v>
       </c>
       <c r="B103" t="n">
         <v>99147</v>
@@ -12027,7 +12024,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12041,10 +12038,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>702016</v>
+        <v>701848</v>
       </c>
       <c r="R103" t="n">
-        <v>6360042</v>
+        <v>6360188</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12107,16 +12104,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317294</t>
+          <t>https://artportalen.se/Sighting/129317281</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137270024</v>
+        <v>129317294</v>
       </c>
       <c r="B104" t="n">
-        <v>99772</v>
+        <v>99147</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12124,37 +12121,46 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219879</v>
+        <v>219864</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Getrams</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Polygonatum odoratum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Mill.) Druce</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>702138</v>
+        <v>702016</v>
       </c>
       <c r="R104" t="n">
-        <v>6360149</v>
+        <v>6360042</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12178,22 +12184,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12204,69 +12200,74 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270024</t>
+          <t>https://artportalen.se/Sighting/129317294</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129317282</v>
+        <v>137270024</v>
       </c>
       <c r="B105" t="n">
-        <v>104639</v>
+        <v>99772</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220164</v>
+        <v>219879</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Getrams</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Polygonatum odoratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Mill.) Druce</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>701991</v>
+        <v>702138</v>
       </c>
       <c r="R105" t="n">
-        <v>6360183</v>
+        <v>6360149</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12290,12 +12291,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12306,36 +12317,31 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317282</t>
+          <t>https://artportalen.se/Sighting/137270024</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129317299</v>
+        <v>129317282</v>
       </c>
       <c r="B106" t="n">
-        <v>102224</v>
+        <v>104639</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12343,46 +12349,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221223</v>
+        <v>220164</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>701900</v>
+        <v>701991</v>
       </c>
       <c r="R106" t="n">
-        <v>6360049</v>
+        <v>6360183</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12442,16 +12439,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317299</t>
+          <t>https://artportalen.se/Sighting/129317282</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120308076</v>
+        <v>129317299</v>
       </c>
       <c r="B107" t="n">
-        <v>107517</v>
+        <v>102224</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12459,34 +12456,43 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221849</v>
+        <v>221223</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:4 (3), Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>701638</v>
+        <v>701900</v>
       </c>
       <c r="R107" t="n">
-        <v>6360226</v>
+        <v>6360049</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12513,12 +12519,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12532,7 +12538,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta i gränsgata.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12543,22 +12549,22 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120308076</t>
+          <t>https://artportalen.se/Sighting/129317299</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129317278</v>
+        <v>120308076</v>
       </c>
       <c r="B108" t="n">
-        <v>107516</v>
+        <v>107517</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12586,17 +12592,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>701841</v>
+        <v>701638</v>
       </c>
       <c r="R108" t="n">
-        <v>6360189</v>
+        <v>6360226</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12620,12 +12626,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12639,7 +12645,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, glänta i gränsgata.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12650,19 +12656,19 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317278</t>
+          <t>https://artportalen.se/Sighting/120308076</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129317285</v>
+        <v>129317278</v>
       </c>
       <c r="B109" t="n">
         <v>107516</v>
@@ -12697,13 +12703,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>702024</v>
+        <v>701841</v>
       </c>
       <c r="R109" t="n">
-        <v>6360122</v>
+        <v>6360189</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12746,7 +12752,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, myrkulle i glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12763,16 +12769,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317285</t>
+          <t>https://artportalen.se/Sighting/129317278</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137271151</v>
+        <v>129317285</v>
       </c>
       <c r="B110" t="n">
-        <v>107866</v>
+        <v>107516</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12800,17 +12806,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>701866</v>
+        <v>702024</v>
       </c>
       <c r="R110" t="n">
-        <v>6359934</v>
+        <v>6360122</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12834,22 +12840,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12860,28 +12856,33 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271151</t>
+          <t>https://artportalen.se/Sighting/129317285</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137271158</v>
+        <v>137271151</v>
       </c>
       <c r="B111" t="n">
         <v>107866</v>
@@ -12916,13 +12917,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>701870</v>
+        <v>701866</v>
       </c>
       <c r="R111" t="n">
-        <v>6359895</v>
+        <v>6359934</v>
       </c>
       <c r="S111" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12951,7 +12952,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12961,7 +12962,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12987,13 +12988,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271158</t>
+          <t>https://artportalen.se/Sighting/137271151</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137273118</v>
+        <v>137271158</v>
       </c>
       <c r="B112" t="n">
         <v>107866</v>
@@ -13024,17 +13025,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>701971</v>
+        <v>701870</v>
       </c>
       <c r="R112" t="n">
-        <v>6359974</v>
+        <v>6359895</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13063,7 +13064,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13073,7 +13074,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13088,24 +13089,24 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273118</t>
+          <t>https://artportalen.se/Sighting/137271158</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>137417995</v>
+        <v>137273118</v>
       </c>
       <c r="B113" t="n">
         <v>107866</v>
@@ -13134,23 +13135,19 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lojsta-Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>701957</v>
+        <v>701971</v>
       </c>
       <c r="R113" t="n">
-        <v>6360053</v>
+        <v>6359974</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13174,12 +13171,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13188,31 +13195,30 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417995</t>
+          <t>https://artportalen.se/Sighting/137273118</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137418044</v>
+        <v>137417995</v>
       </c>
       <c r="B114" t="n">
         <v>107866</v>
@@ -13251,10 +13257,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>702256</v>
+        <v>701957</v>
       </c>
       <c r="R114" t="n">
-        <v>6360187</v>
+        <v>6360053</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13313,16 +13319,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137418044</t>
+          <t>https://artportalen.se/Sighting/137417995</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129317277</v>
+        <v>137418044</v>
       </c>
       <c r="B115" t="n">
-        <v>102559</v>
+        <v>107866</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13330,16 +13336,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222133</v>
+        <v>221849</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -13348,16 +13354,20 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Lojsta-Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>701841</v>
+        <v>702256</v>
       </c>
       <c r="R115" t="n">
-        <v>6360189</v>
+        <v>6360187</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13384,12 +13394,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13398,76 +13408,72 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317277</t>
+          <t>https://artportalen.se/Sighting/137418044</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137268903</v>
+        <v>129317277</v>
       </c>
       <c r="B116" t="n">
-        <v>87509</v>
+        <v>102559</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>248956</v>
+        <v>222133</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>701940</v>
+        <v>701841</v>
       </c>
       <c r="R116" t="n">
-        <v>6360261</v>
+        <v>6360189</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13491,22 +13497,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13517,28 +13513,33 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268903</t>
+          <t>https://artportalen.se/Sighting/129317277</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137268906</v>
+        <v>137268903</v>
       </c>
       <c r="B117" t="n">
         <v>87509</v>
@@ -13573,10 +13574,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>702007</v>
+        <v>701940</v>
       </c>
       <c r="R117" t="n">
-        <v>6360245</v>
+        <v>6360261</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13608,7 +13609,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13618,7 +13619,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13644,13 +13645,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268906</t>
+          <t>https://artportalen.se/Sighting/137268903</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137268908</v>
+        <v>137268906</v>
       </c>
       <c r="B118" t="n">
         <v>87509</v>
@@ -13685,10 +13686,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>702084</v>
+        <v>702007</v>
       </c>
       <c r="R118" t="n">
-        <v>6360207</v>
+        <v>6360245</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13720,7 +13721,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13730,7 +13731,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13756,13 +13757,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268908</t>
+          <t>https://artportalen.se/Sighting/137268906</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137270010</v>
+        <v>137268908</v>
       </c>
       <c r="B119" t="n">
         <v>87509</v>
@@ -13793,14 +13794,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>701672</v>
+        <v>702084</v>
       </c>
       <c r="R119" t="n">
-        <v>6360193</v>
+        <v>6360207</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13832,7 +13833,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13842,7 +13843,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13857,24 +13858,24 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270010</t>
+          <t>https://artportalen.se/Sighting/137268908</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137270029</v>
+        <v>137270010</v>
       </c>
       <c r="B120" t="n">
         <v>87509</v>
@@ -13909,13 +13910,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>701955</v>
+        <v>701672</v>
       </c>
       <c r="R120" t="n">
-        <v>6359965</v>
+        <v>6360193</v>
       </c>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13944,7 +13945,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13954,7 +13955,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13980,13 +13981,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270029</t>
+          <t>https://artportalen.se/Sighting/137270010</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137270033</v>
+        <v>137270029</v>
       </c>
       <c r="B121" t="n">
         <v>87509</v>
@@ -14021,13 +14022,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>701979</v>
+        <v>701955</v>
       </c>
       <c r="R121" t="n">
-        <v>6359708</v>
+        <v>6359965</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14056,7 +14057,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14066,7 +14067,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14092,13 +14093,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270033</t>
+          <t>https://artportalen.se/Sighting/137270029</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137271152</v>
+        <v>137270033</v>
       </c>
       <c r="B122" t="n">
         <v>87509</v>
@@ -14129,17 +14130,17 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>701893</v>
+        <v>701979</v>
       </c>
       <c r="R122" t="n">
-        <v>6359964</v>
+        <v>6359708</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14168,7 +14169,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14178,7 +14179,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14193,24 +14194,24 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271152</t>
+          <t>https://artportalen.se/Sighting/137270033</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137271155</v>
+        <v>137271152</v>
       </c>
       <c r="B123" t="n">
         <v>87509</v>
@@ -14245,13 +14246,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>701880</v>
+        <v>701893</v>
       </c>
       <c r="R123" t="n">
-        <v>6359914</v>
+        <v>6359964</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14280,7 +14281,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14290,7 +14291,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14316,13 +14317,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271155</t>
+          <t>https://artportalen.se/Sighting/137271152</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137271156</v>
+        <v>137271155</v>
       </c>
       <c r="B124" t="n">
         <v>87509</v>
@@ -14357,10 +14358,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>701870</v>
+        <v>701880</v>
       </c>
       <c r="R124" t="n">
-        <v>6359909</v>
+        <v>6359914</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14392,7 +14393,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14402,7 +14403,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14428,13 +14429,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271156</t>
+          <t>https://artportalen.se/Sighting/137271155</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>137271161</v>
+        <v>137271156</v>
       </c>
       <c r="B125" t="n">
         <v>87509</v>
@@ -14469,10 +14470,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>701825</v>
+        <v>701870</v>
       </c>
       <c r="R125" t="n">
-        <v>6359917</v>
+        <v>6359909</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14504,7 +14505,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14514,7 +14515,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14540,13 +14541,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271161</t>
+          <t>https://artportalen.se/Sighting/137271156</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>137271164</v>
+        <v>137271161</v>
       </c>
       <c r="B126" t="n">
         <v>87509</v>
@@ -14581,10 +14582,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>701805</v>
+        <v>701825</v>
       </c>
       <c r="R126" t="n">
-        <v>6359870</v>
+        <v>6359917</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14616,7 +14617,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14626,7 +14627,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14652,13 +14653,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271164</t>
+          <t>https://artportalen.se/Sighting/137271161</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>137271190</v>
+        <v>137271164</v>
       </c>
       <c r="B127" t="n">
         <v>87509</v>
@@ -14693,13 +14694,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>702072</v>
+        <v>701805</v>
       </c>
       <c r="R127" t="n">
-        <v>6359750</v>
+        <v>6359870</v>
       </c>
       <c r="S127" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14728,7 +14729,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14738,7 +14739,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14764,13 +14765,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271190</t>
+          <t>https://artportalen.se/Sighting/137271164</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>137273111</v>
+        <v>137271190</v>
       </c>
       <c r="B128" t="n">
         <v>87509</v>
@@ -14801,17 +14802,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>701885</v>
+        <v>702072</v>
       </c>
       <c r="R128" t="n">
-        <v>6360024</v>
+        <v>6359750</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14840,7 +14841,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14850,7 +14851,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14865,24 +14866,24 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273111</t>
+          <t>https://artportalen.se/Sighting/137271190</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>137287622</v>
+        <v>137273111</v>
       </c>
       <c r="B129" t="n">
         <v>87509</v>
@@ -14913,14 +14914,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>701795</v>
+        <v>701885</v>
       </c>
       <c r="R129" t="n">
-        <v>6360098</v>
+        <v>6360024</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14947,22 +14948,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14977,24 +14978,24 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137287622</t>
+          <t>https://artportalen.se/Sighting/137273111</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>137292000</v>
+        <v>137287622</v>
       </c>
       <c r="B130" t="n">
         <v>87509</v>
@@ -15029,13 +15030,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>701803</v>
+        <v>701795</v>
       </c>
       <c r="R130" t="n">
-        <v>6360093</v>
+        <v>6360098</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15064,7 +15065,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15074,7 +15075,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15089,24 +15090,24 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292000</t>
+          <t>https://artportalen.se/Sighting/137287622</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>137292001</v>
+        <v>137292000</v>
       </c>
       <c r="B131" t="n">
         <v>87509</v>
@@ -15141,10 +15142,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>701785</v>
+        <v>701803</v>
       </c>
       <c r="R131" t="n">
-        <v>6360090</v>
+        <v>6360093</v>
       </c>
       <c r="S131" t="n">
         <v>6</v>
@@ -15176,7 +15177,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15186,7 +15187,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15206,19 +15207,19 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137292001</t>
+          <t>https://artportalen.se/Sighting/137292000</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>137313534</v>
+        <v>137292001</v>
       </c>
       <c r="B132" t="n">
         <v>87509</v>
@@ -15249,17 +15250,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>701741</v>
+        <v>701785</v>
       </c>
       <c r="R132" t="n">
-        <v>6359935</v>
+        <v>6360090</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15278,7 +15279,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -15288,7 +15289,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15298,7 +15299,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15313,24 +15314,24 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg, Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313534</t>
+          <t>https://artportalen.se/Sighting/137292001</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>137313539</v>
+        <v>137313534</v>
       </c>
       <c r="B133" t="n">
         <v>87509</v>
@@ -15365,10 +15366,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>701839</v>
+        <v>701741</v>
       </c>
       <c r="R133" t="n">
-        <v>6360044</v>
+        <v>6359935</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15390,7 +15391,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -15400,7 +15401,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15410,7 +15411,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15436,13 +15437,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313539</t>
+          <t>https://artportalen.se/Sighting/137313534</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>137313542</v>
+        <v>137313539</v>
       </c>
       <c r="B134" t="n">
         <v>87509</v>
@@ -15477,10 +15478,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>701933</v>
+        <v>701839</v>
       </c>
       <c r="R134" t="n">
-        <v>6360160</v>
+        <v>6360044</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15512,7 +15513,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15522,7 +15523,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15548,13 +15549,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313542</t>
+          <t>https://artportalen.se/Sighting/137313539</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>137313544</v>
+        <v>137313542</v>
       </c>
       <c r="B135" t="n">
         <v>87509</v>
@@ -15589,10 +15590,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>701806</v>
+        <v>701933</v>
       </c>
       <c r="R135" t="n">
-        <v>6360084</v>
+        <v>6360160</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15624,7 +15625,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15634,7 +15635,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15660,13 +15661,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313544</t>
+          <t>https://artportalen.se/Sighting/137313542</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>137417406</v>
+        <v>137313544</v>
       </c>
       <c r="B136" t="n">
         <v>87509</v>
@@ -15697,17 +15698,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>701816</v>
+        <v>701806</v>
       </c>
       <c r="R136" t="n">
-        <v>6360135</v>
+        <v>6360084</v>
       </c>
       <c r="S136" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15731,22 +15732,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15761,24 +15762,24 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417406</t>
+          <t>https://artportalen.se/Sighting/137313544</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>137417421</v>
+        <v>137417406</v>
       </c>
       <c r="B137" t="n">
         <v>87509</v>
@@ -15813,13 +15814,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>701980</v>
+        <v>701816</v>
       </c>
       <c r="R137" t="n">
-        <v>6360171</v>
+        <v>6360135</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15848,7 +15849,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15858,7 +15859,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15884,13 +15885,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417421</t>
+          <t>https://artportalen.se/Sighting/137417406</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>137417436</v>
+        <v>137417421</v>
       </c>
       <c r="B138" t="n">
         <v>87509</v>
@@ -15925,13 +15926,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>702050</v>
+        <v>701980</v>
       </c>
       <c r="R138" t="n">
-        <v>6360283</v>
+        <v>6360171</v>
       </c>
       <c r="S138" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15960,7 +15961,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15970,7 +15971,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15979,7 +15980,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15997,13 +15997,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417436</t>
+          <t>https://artportalen.se/Sighting/137417421</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>137417438</v>
+        <v>137417436</v>
       </c>
       <c r="B139" t="n">
         <v>87509</v>
@@ -16038,10 +16038,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>702120</v>
+        <v>702050</v>
       </c>
       <c r="R139" t="n">
-        <v>6360326</v>
+        <v>6360283</v>
       </c>
       <c r="S139" t="n">
         <v>7</v>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16110,36 +16110,40 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417438</t>
+          <t>https://artportalen.se/Sighting/137417436</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>137417404</v>
+        <v>137417438</v>
       </c>
       <c r="B140" t="n">
-        <v>87665</v>
+        <v>87509</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>249249</v>
+        <v>248956</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grynspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius olidoamethysteus s.lat.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -16147,13 +16151,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>701760</v>
+        <v>702120</v>
       </c>
       <c r="R140" t="n">
-        <v>6360146</v>
+        <v>6360326</v>
       </c>
       <c r="S140" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16182,7 +16186,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16192,7 +16196,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16219,13 +16223,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417404</t>
+          <t>https://artportalen.se/Sighting/137417438</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>137417431</v>
+        <v>137417404</v>
       </c>
       <c r="B141" t="n">
         <v>87665</v>
@@ -16256,13 +16260,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>701907</v>
+        <v>701760</v>
       </c>
       <c r="R141" t="n">
-        <v>6360355</v>
+        <v>6360146</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16291,7 +16295,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16301,7 +16305,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16328,51 +16332,47 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417431</t>
+          <t>https://artportalen.se/Sighting/137417404</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>137268910</v>
+        <v>137417431</v>
       </c>
       <c r="B142" t="n">
-        <v>87345</v>
+        <v>87665</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>249278</v>
+        <v>249249</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Grynspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>(Pers.) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius olidoamethysteus s.lat.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>702067</v>
+        <v>701907</v>
       </c>
       <c r="R142" t="n">
-        <v>6360071</v>
+        <v>6360355</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16399,22 +16399,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16423,33 +16423,34 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137268910</t>
+          <t>https://artportalen.se/Sighting/137417431</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>137271131</v>
+        <v>137268910</v>
       </c>
       <c r="B143" t="n">
-        <v>87593</v>
+        <v>87345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16457,37 +16458,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lojsta Graunvik, Gtl</t>
+          <t>Lojsta Bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>701753</v>
+        <v>702067</v>
       </c>
       <c r="R143" t="n">
-        <v>6359975</v>
+        <v>6360071</v>
       </c>
       <c r="S143" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16516,7 +16517,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16526,7 +16527,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16541,24 +16542,24 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271131</t>
+          <t>https://artportalen.se/Sighting/137268910</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>137271132</v>
+        <v>137271131</v>
       </c>
       <c r="B144" t="n">
         <v>87593</v>
@@ -16593,13 +16594,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>701759</v>
+        <v>701753</v>
       </c>
       <c r="R144" t="n">
-        <v>6359980</v>
+        <v>6359975</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16628,7 +16629,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16638,7 +16639,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16664,13 +16665,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271132</t>
+          <t>https://artportalen.se/Sighting/137271131</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>137271138</v>
+        <v>137271132</v>
       </c>
       <c r="B145" t="n">
         <v>87593</v>
@@ -16705,13 +16706,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>701781</v>
+        <v>701759</v>
       </c>
       <c r="R145" t="n">
-        <v>6360015</v>
+        <v>6359980</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16740,7 +16741,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16750,7 +16751,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16776,13 +16777,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271138</t>
+          <t>https://artportalen.se/Sighting/137271132</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>137271141</v>
+        <v>137271138</v>
       </c>
       <c r="B146" t="n">
         <v>87593</v>
@@ -16817,10 +16818,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>701799</v>
+        <v>701781</v>
       </c>
       <c r="R146" t="n">
-        <v>6360005</v>
+        <v>6360015</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16852,7 +16853,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16862,7 +16863,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16888,13 +16889,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271141</t>
+          <t>https://artportalen.se/Sighting/137271138</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>137271144</v>
+        <v>137271141</v>
       </c>
       <c r="B147" t="n">
         <v>87593</v>
@@ -16929,10 +16930,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>701811</v>
+        <v>701799</v>
       </c>
       <c r="R147" t="n">
-        <v>6359992</v>
+        <v>6360005</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16964,7 +16965,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16974,7 +16975,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17000,13 +17001,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271144</t>
+          <t>https://artportalen.se/Sighting/137271141</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>137271148</v>
+        <v>137271144</v>
       </c>
       <c r="B148" t="n">
         <v>87593</v>
@@ -17041,10 +17042,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>701797</v>
+        <v>701811</v>
       </c>
       <c r="R148" t="n">
-        <v>6359967</v>
+        <v>6359992</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -17076,7 +17077,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17086,7 +17087,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17112,13 +17113,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271148</t>
+          <t>https://artportalen.se/Sighting/137271144</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>137271154</v>
+        <v>137271148</v>
       </c>
       <c r="B149" t="n">
         <v>87593</v>
@@ -17153,10 +17154,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>701903</v>
+        <v>701797</v>
       </c>
       <c r="R149" t="n">
-        <v>6359923</v>
+        <v>6359967</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -17188,7 +17189,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17198,7 +17199,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17224,13 +17225,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271154</t>
+          <t>https://artportalen.se/Sighting/137271148</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>137271166</v>
+        <v>137271154</v>
       </c>
       <c r="B150" t="n">
         <v>87593</v>
@@ -17265,13 +17266,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>701876</v>
+        <v>701903</v>
       </c>
       <c r="R150" t="n">
-        <v>6359811</v>
+        <v>6359923</v>
       </c>
       <c r="S150" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17300,7 +17301,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17310,7 +17311,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17336,13 +17337,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271166</t>
+          <t>https://artportalen.se/Sighting/137271154</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>137271167</v>
+        <v>137271166</v>
       </c>
       <c r="B151" t="n">
         <v>87593</v>
@@ -17377,13 +17378,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>701880</v>
+        <v>701876</v>
       </c>
       <c r="R151" t="n">
-        <v>6359800</v>
+        <v>6359811</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17412,7 +17413,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17422,7 +17423,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17448,13 +17449,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271167</t>
+          <t>https://artportalen.se/Sighting/137271166</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>137271171</v>
+        <v>137271167</v>
       </c>
       <c r="B152" t="n">
         <v>87593</v>
@@ -17489,10 +17490,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>701863</v>
+        <v>701880</v>
       </c>
       <c r="R152" t="n">
-        <v>6359808</v>
+        <v>6359800</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17524,7 +17525,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17534,7 +17535,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17560,13 +17561,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271171</t>
+          <t>https://artportalen.se/Sighting/137271167</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>137271172</v>
+        <v>137271171</v>
       </c>
       <c r="B153" t="n">
         <v>87593</v>
@@ -17601,10 +17602,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>701835</v>
+        <v>701863</v>
       </c>
       <c r="R153" t="n">
-        <v>6359815</v>
+        <v>6359808</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -17636,7 +17637,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17646,7 +17647,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17672,13 +17673,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271172</t>
+          <t>https://artportalen.se/Sighting/137271171</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>137271178</v>
+        <v>137271172</v>
       </c>
       <c r="B154" t="n">
         <v>87593</v>
@@ -17713,10 +17714,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>701848</v>
+        <v>701835</v>
       </c>
       <c r="R154" t="n">
-        <v>6359748</v>
+        <v>6359815</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17748,7 +17749,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17758,7 +17759,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17784,13 +17785,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271178</t>
+          <t>https://artportalen.se/Sighting/137271172</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>137271179</v>
+        <v>137271178</v>
       </c>
       <c r="B155" t="n">
         <v>87593</v>
@@ -17825,10 +17826,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>701892</v>
+        <v>701848</v>
       </c>
       <c r="R155" t="n">
-        <v>6359714</v>
+        <v>6359748</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17860,7 +17861,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17870,7 +17871,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17896,13 +17897,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271179</t>
+          <t>https://artportalen.se/Sighting/137271178</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>137271186</v>
+        <v>137271179</v>
       </c>
       <c r="B156" t="n">
         <v>87593</v>
@@ -17937,10 +17938,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>702010</v>
+        <v>701892</v>
       </c>
       <c r="R156" t="n">
-        <v>6359709</v>
+        <v>6359714</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17972,7 +17973,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17982,7 +17983,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18008,13 +18009,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271186</t>
+          <t>https://artportalen.se/Sighting/137271179</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>137271187</v>
+        <v>137271186</v>
       </c>
       <c r="B157" t="n">
         <v>87593</v>
@@ -18049,10 +18050,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>702019</v>
+        <v>702010</v>
       </c>
       <c r="R157" t="n">
-        <v>6359713</v>
+        <v>6359709</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18084,7 +18085,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18094,7 +18095,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18120,13 +18121,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271187</t>
+          <t>https://artportalen.se/Sighting/137271186</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>137273108</v>
+        <v>137271187</v>
       </c>
       <c r="B158" t="n">
         <v>87593</v>
@@ -18157,14 +18158,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>701798</v>
+        <v>702019</v>
       </c>
       <c r="R158" t="n">
-        <v>6359990</v>
+        <v>6359713</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18196,7 +18197,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18206,7 +18207,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18215,31 +18216,30 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273108</t>
+          <t>https://artportalen.se/Sighting/137271187</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>137273112</v>
+        <v>137273108</v>
       </c>
       <c r="B159" t="n">
         <v>87593</v>
@@ -18274,10 +18274,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>701879</v>
+        <v>701798</v>
       </c>
       <c r="R159" t="n">
-        <v>6360033</v>
+        <v>6359990</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18319,7 +18319,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18346,13 +18346,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273112</t>
+          <t>https://artportalen.se/Sighting/137273108</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>137291062</v>
+        <v>137273112</v>
       </c>
       <c r="B160" t="n">
         <v>87593</v>
@@ -18381,19 +18381,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>701909</v>
+        <v>701879</v>
       </c>
       <c r="R160" t="n">
-        <v>6359993</v>
+        <v>6360033</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -18420,12 +18417,22 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18441,24 +18448,24 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291062</t>
+          <t>https://artportalen.se/Sighting/137273112</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>137291108</v>
+        <v>137291062</v>
       </c>
       <c r="B161" t="n">
         <v>87593</v>
@@ -18492,17 +18499,17 @@
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>701834</v>
+        <v>701909</v>
       </c>
       <c r="R161" t="n">
-        <v>6360076</v>
+        <v>6359993</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18529,19 +18536,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18557,24 +18554,24 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291108</t>
+          <t>https://artportalen.se/Sighting/137291062</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>137291113</v>
+        <v>137291108</v>
       </c>
       <c r="B162" t="n">
         <v>87593</v>
@@ -18612,13 +18609,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>701956</v>
+        <v>701834</v>
       </c>
       <c r="R162" t="n">
-        <v>6360176</v>
+        <v>6360076</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18647,7 +18644,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18657,7 +18654,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18684,13 +18681,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291113</t>
+          <t>https://artportalen.se/Sighting/137291108</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>137291120</v>
+        <v>137291113</v>
       </c>
       <c r="B163" t="n">
         <v>87593</v>
@@ -18728,10 +18725,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>701985</v>
+        <v>701956</v>
       </c>
       <c r="R163" t="n">
-        <v>6360293</v>
+        <v>6360176</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18763,7 +18760,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18773,7 +18770,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18800,13 +18797,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291120</t>
+          <t>https://artportalen.se/Sighting/137291113</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>137312001</v>
+        <v>137291120</v>
       </c>
       <c r="B164" t="n">
         <v>87593</v>
@@ -18834,31 +18831,23 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Lojsta hed, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>701745</v>
+        <v>701985</v>
       </c>
       <c r="R164" t="n">
-        <v>6359957</v>
+        <v>6360293</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18885,9 +18874,19 @@
           <t>2026-10-16</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18903,24 +18902,24 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson, Nicolai Berg, Meandra Sewell</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137312001</t>
+          <t>https://artportalen.se/Sighting/137291120</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>137313535</v>
+        <v>137312001</v>
       </c>
       <c r="B165" t="n">
         <v>87593</v>
@@ -18948,20 +18947,31 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>701758</v>
+        <v>701745</v>
       </c>
       <c r="R165" t="n">
-        <v>6359921</v>
+        <v>6359957</v>
       </c>
       <c r="S165" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18988,19 +18998,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19016,24 +19016,24 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Oskar Karl Elias Olsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Oskar Karl Elias Olsson, Nicolai Berg, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137313535</t>
+          <t>https://artportalen.se/Sighting/137312001</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>137417398</v>
+        <v>137313535</v>
       </c>
       <c r="B166" t="n">
         <v>87593</v>
@@ -19064,17 +19064,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta bjärs, Gtl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>701709</v>
+        <v>701758</v>
       </c>
       <c r="R166" t="n">
-        <v>6360231</v>
+        <v>6359921</v>
       </c>
       <c r="S166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19098,22 +19098,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19129,24 +19129,24 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417398</t>
+          <t>https://artportalen.se/Sighting/137313535</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>137417401</v>
+        <v>137417398</v>
       </c>
       <c r="B167" t="n">
         <v>87593</v>
@@ -19181,13 +19181,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>701788</v>
+        <v>701709</v>
       </c>
       <c r="R167" t="n">
-        <v>6360223</v>
+        <v>6360231</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19253,13 +19253,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417401</t>
+          <t>https://artportalen.se/Sighting/137417398</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>137417417</v>
+        <v>137417401</v>
       </c>
       <c r="B168" t="n">
         <v>87593</v>
@@ -19294,13 +19294,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>701932</v>
+        <v>701788</v>
       </c>
       <c r="R168" t="n">
-        <v>6360113</v>
+        <v>6360223</v>
       </c>
       <c r="S168" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19366,13 +19366,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417417</t>
+          <t>https://artportalen.se/Sighting/137417401</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>137417423</v>
+        <v>137417417</v>
       </c>
       <c r="B169" t="n">
         <v>87593</v>
@@ -19407,13 +19407,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>701952</v>
+        <v>701932</v>
       </c>
       <c r="R169" t="n">
-        <v>6360217</v>
+        <v>6360113</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19479,13 +19479,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417423</t>
+          <t>https://artportalen.se/Sighting/137417417</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>137417424</v>
+        <v>137417423</v>
       </c>
       <c r="B170" t="n">
         <v>87593</v>
@@ -19520,13 +19520,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>701918</v>
+        <v>701952</v>
       </c>
       <c r="R170" t="n">
-        <v>6360249</v>
+        <v>6360217</v>
       </c>
       <c r="S170" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19592,13 +19592,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417424</t>
+          <t>https://artportalen.se/Sighting/137417423</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>137417428</v>
+        <v>137417424</v>
       </c>
       <c r="B171" t="n">
         <v>87593</v>
@@ -19633,13 +19633,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>701891</v>
+        <v>701918</v>
       </c>
       <c r="R171" t="n">
-        <v>6360324</v>
+        <v>6360249</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19705,13 +19705,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417428</t>
+          <t>https://artportalen.se/Sighting/137417424</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>137417458</v>
+        <v>137417428</v>
       </c>
       <c r="B172" t="n">
         <v>87593</v>
@@ -19746,13 +19746,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>701882</v>
+        <v>701891</v>
       </c>
       <c r="R172" t="n">
-        <v>6359991</v>
+        <v>6360324</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19818,16 +19818,16 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417458</t>
+          <t>https://artportalen.se/Sighting/137417428</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>97356373</v>
+        <v>137417458</v>
       </c>
       <c r="B173" t="n">
-        <v>87312</v>
+        <v>87593</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19835,37 +19835,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>701965</v>
+        <v>701882</v>
       </c>
       <c r="R173" t="n">
-        <v>6359889</v>
+        <v>6359991</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19892,12 +19889,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19913,74 +19920,68 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97356373</t>
+          <t>https://artportalen.se/Sighting/137417458</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129317287</v>
+        <v>97356373</v>
       </c>
       <c r="B174" t="n">
-        <v>103385</v>
+        <v>87312</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6037533</v>
+        <v>6037417</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>702037</v>
+        <v>701965</v>
       </c>
       <c r="R174" t="n">
-        <v>6360098</v>
+        <v>6359889</v>
       </c>
       <c r="S174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20004,17 +20005,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20023,35 +20019,31 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317287</t>
+          <t>https://artportalen.se/Sighting/97356373</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129317290</v>
+        <v>129317287</v>
       </c>
       <c r="B175" t="n">
         <v>103385</v>
@@ -20095,10 +20087,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>701998</v>
+        <v>702037</v>
       </c>
       <c r="R175" t="n">
-        <v>6360055</v>
+        <v>6360098</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -20166,13 +20158,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317290</t>
+          <t>https://artportalen.se/Sighting/129317287</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129317293</v>
+        <v>129317290</v>
       </c>
       <c r="B176" t="n">
         <v>103385</v>
@@ -20216,10 +20208,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>702001</v>
+        <v>701998</v>
       </c>
       <c r="R176" t="n">
-        <v>6360045</v>
+        <v>6360055</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -20256,7 +20248,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>30 cm hög, steil.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20287,13 +20279,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317293</t>
+          <t>https://artportalen.se/Sighting/129317290</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129317303</v>
+        <v>129317293</v>
       </c>
       <c r="B177" t="n">
         <v>103385</v>
@@ -20337,10 +20329,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>701855</v>
+        <v>702001</v>
       </c>
       <c r="R177" t="n">
-        <v>6360068</v>
+        <v>6360045</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -20377,7 +20369,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>40 cm hög, steil.</t>
+          <t>30 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20408,13 +20400,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317303</t>
+          <t>https://artportalen.se/Sighting/129317293</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129317304</v>
+        <v>129317303</v>
       </c>
       <c r="B178" t="n">
         <v>103385</v>
@@ -20458,10 +20450,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>701837</v>
+        <v>701855</v>
       </c>
       <c r="R178" t="n">
-        <v>6360008</v>
+        <v>6360068</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20529,13 +20521,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317304</t>
+          <t>https://artportalen.se/Sighting/129317303</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129317307</v>
+        <v>129317304</v>
       </c>
       <c r="B179" t="n">
         <v>103385</v>
@@ -20579,13 +20571,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>701807</v>
+        <v>701837</v>
       </c>
       <c r="R179" t="n">
-        <v>6359985</v>
+        <v>6360008</v>
       </c>
       <c r="S179" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20619,7 +20611,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
+          <t>40 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20650,13 +20642,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317307</t>
+          <t>https://artportalen.se/Sighting/129317304</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129317312</v>
+        <v>129317307</v>
       </c>
       <c r="B180" t="n">
         <v>103385</v>
@@ -20700,10 +20692,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>701777</v>
+        <v>701807</v>
       </c>
       <c r="R180" t="n">
-        <v>6360000</v>
+        <v>6359985</v>
       </c>
       <c r="S180" t="n">
         <v>3</v>
@@ -20740,7 +20732,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20771,13 +20763,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317312</t>
+          <t>https://artportalen.se/Sighting/129317307</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129317313</v>
+        <v>129317312</v>
       </c>
       <c r="B181" t="n">
         <v>103385</v>
@@ -20821,10 +20813,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>701778</v>
+        <v>701777</v>
       </c>
       <c r="R181" t="n">
-        <v>6359998</v>
+        <v>6360000</v>
       </c>
       <c r="S181" t="n">
         <v>3</v>
@@ -20861,7 +20853,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>50 cm hög, steil.</t>
+          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20892,16 +20884,16 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129317313</t>
+          <t>https://artportalen.se/Sighting/129317312</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>137417408</v>
+        <v>129317313</v>
       </c>
       <c r="B182" t="n">
-        <v>87621</v>
+        <v>103385</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20909,40 +20901,46 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6052416</v>
+        <v>6037533</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fågelträcksspindling</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cortinarius subrugulosus</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Bidaud &amp; Armada</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>701889</v>
+        <v>701778</v>
       </c>
       <c r="R182" t="n">
-        <v>6360152</v>
+        <v>6359998</v>
       </c>
       <c r="S182" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20966,55 +20964,54 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF182" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG182" t="b">
         <v>0</v>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417408</t>
+          <t>https://artportalen.se/Sighting/129317313</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>137417419</v>
+        <v>137417408</v>
       </c>
       <c r="B183" t="n">
         <v>87621</v>
@@ -21043,19 +21040,22 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Lojsta Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>701930</v>
+        <v>701889</v>
       </c>
       <c r="R183" t="n">
-        <v>6360128</v>
+        <v>6360152</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -21094,12 +21094,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Fågelskit på hatten, orange KOH-reaktion på hatt, vitt BM, negativ på BM.</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21126,13 +21121,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417419</t>
+          <t>https://artportalen.se/Sighting/137417408</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>137417422</v>
+        <v>137417419</v>
       </c>
       <c r="B184" t="n">
         <v>87621</v>
@@ -21167,13 +21162,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>701994</v>
+        <v>701930</v>
       </c>
       <c r="R184" t="n">
-        <v>6360164</v>
+        <v>6360128</v>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21202,7 +21197,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21212,14 +21207,19 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Fågelskit på hatten, orange KOH-reaktion på hatt, vitt BM, negativ på BM.</t>
         </is>
       </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
       <c r="AE184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
@@ -21239,13 +21239,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137417422</t>
+          <t>https://artportalen.se/Sighting/137417419</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>137417443</v>
+        <v>137417422</v>
       </c>
       <c r="B185" t="n">
         <v>87621</v>
@@ -21280,13 +21280,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>702306</v>
+        <v>701994</v>
       </c>
       <c r="R185" t="n">
-        <v>6360310</v>
+        <v>6360164</v>
       </c>
       <c r="S185" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21325,14 +21325,14 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
@@ -21351,6 +21351,119 @@
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137417422</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>137417443</v>
+      </c>
+      <c r="B186" t="n">
+        <v>87621</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6052416</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Fågelträcksspindling</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Cortinarius subrugulosus</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Bidaud &amp; Armada</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Lojsta Ase, Stangsmyr V, Gtl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>702306</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6360310</v>
+      </c>
+      <c r="S186" t="n">
+        <v>7</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137417443</t>
         </is>
@@ -21542,6 +21655,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
